--- a/execution-plan/MRC-CONTROL-ACTION-RACI-MATRIX.xlsx
+++ b/execution-plan/MRC-CONTROL-ACTION-RACI-MATRIX.xlsx
@@ -529,13 +529,13 @@
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. Run Get-ADComputer -Filter * and Get-ADUser -Filter * with relevant properties to export the current AD-joined device and account roster.
+2. In the ePO console, generate the Asset/Software Inventory report for all managed endpoints and export to CSV.
+3. Cross-reference the ePO software inventory against the CM-8 authorized baseline/hardware-software list to identify unauthorized or missing components.
+4. Query ePO Product Deployment/Policy Compliance data for any user-installed software not on the approved application whitelist per CM-11.
+5. Open a CCB change ticket for any unauthorized software or hardware found and track to removal or approval.
+6. Update the system component inventory baseline in the configuration management database with the reconciled results.
+7. Export the reconciliation report and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -568,13 +568,12 @@
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. Open the Splunk security dashboard for the system and review the current alert queue for SI-4 monitoring events (IDS/IPS, boundary, and endpoint alerts).
+2. Review ePO Threat Event Log for the reporting period for malicious-activity detections requiring analyst triage.
+3. Document analyst disposition (false positive, contained, escalated) for each unresolved alert in the SOC ticketing system.
+4. Confirm Splunk data inputs and forwarders for monitored log sources show active, uninterrupted collection with no gaps.
+5. Brief the ISSO on any unresolved or escalated monitoring findings from the period via meeting minutes/decision record.
+6. File the Splunk dashboard export and meeting minutes in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -607,13 +606,12 @@
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. In the ePO console, confirm On-Access Scan policy is enabled and enforced on all managed endpoints via the Policy Compliance query.
+2. Verify DAT/engine signature version dashboard shows current definitions deployed within the required update window across all endpoints.
+3. Review the ePO Threat Event Log for real-time detections on externally sourced files (removable media, email attachments, downloads) during the period.
+4. Confirm quarantine/remediation actions were completed for each detected threat by checking the Threat Event Log disposition status.
+5. Identify and remediate any endpoint reporting an outdated DAT version or disabled on-access scanning via an Agent Wake-Up call.
+6. Export the ePO Policy Compliance and Threat Event Log reports and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -654,12 +652,13 @@
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Pattern C — Update / Patch / Signature Refresh
-1. Query the authoritative source (vendor/DISA/NVD advisory feed mirrored locally, or the local update-management tool) for the current required version/signature/key state.
-2. Compare the authoritative current state against the deployed state.
-3. Apply the update through the organization's change-control process (per `execution-plan/ROLE-CROSSWALK.md`'s CCB routing where the update is configuration-relevant).
-4. Verify the update took effect (re-query deployed state).
-5. Log cycle completion (date, prior version, new version, verifier) in the repository location specified in the Task Index.</t>
+          <t>1. Run a Nessus credentialed vulnerability scan against the system using the current IAVM-mapped plugin feed.
+2. Export the Nessus scan results and filter findings by IAVM notice number to identify open IAVA/IAVB/TA compliance gaps.
+3. Cross-check outstanding IAVM directives against WSUS update deployment status to confirm patches have been pushed to affected hosts.
+4. Deploy any missing patches via WSUS and re-scan affected hosts with Nessus to confirm remediation (SI-2).
+5. For findings that cannot be remediated within the directive's compliance window, create or update the corresponding POA&amp;M entry per CA-5.
+6. Update the POA&amp;M tracker with revised milestones and residual risk acceptance status for any open items.
+7. Export the Nessus rescan report and POA&amp;M update and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -704,13 +703,12 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. Run Get-ADGroupMember against privileged AD security groups to verify current membership matches the approved access list (AC-6).
+2. Run gpresult /h against a sample of workstations/servers to confirm the GPO enforcing session lock timeout and screen-lock policy is applied (AC-11).
+3. Review Local Security Policy / Security Configuration and Analysis snap-in settings for session termination thresholds and confirm they match the SSP-defined values (AC-12).
+4. Query auditpol /get to confirm access-enforcement-related audit subcategories (logon, privilege use, object access) are enabled per AC-3.
+5. Identify any accounts with excess privilege or stale group membership and submit an access-removal ticket to the System Administrator.
+6. Export the Get-ADGroupMember and gpresult outputs and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -747,13 +745,12 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. Open the Splunk SIEM dashboard and review the audit storage capacity saved search/alert for all in-scope log-source indexes (AU-4).
+2. Confirm current index disk utilization is below the configured warning threshold and review retention/rollover settings for each index.
+3. Run the Splunk saved search for audit processing-failure events (forwarder disconnects, indexing queue blocks, dropped events) for the reporting period (AU-5).
+4. Investigate and document root cause and resolution for any processing-failure alert triggered during the period.
+5. Adjust index storage allocation or retention policy if utilization trend projects a threshold breach before the next review cycle.
+6. Export the Splunk capacity and processing-failure dashboard reports and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -786,13 +783,12 @@
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. Review Windows Defender Firewall with Advanced Security inbound/outbound rule sets on boundary-facing servers against the approved firewall rule baseline.
+2. Confirm IPsec policy configuration enforcing encrypted boundary connections matches the SSP-defined boundary protection design.
+3. Run a Nessus scan against boundary devices/servers to identify unauthorized open ports or services exposed across the boundary.
+4. If Trellix/McAfee network security modules are deployed, review their policy compliance status for boundary-related rule enforcement.
+5. Remediate any unauthorized rule, open port, or policy drift found by submitting a change ticket through the Network Administrator.
+6. Export the firewall rule review and Nessus scan results and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -825,13 +821,12 @@
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. Run manage-bde -status on a sample of in-scope servers/workstations to confirm BitLocker (or equivalent FIPS-validated encryption) is enabled on all data volumes.
+2. Verify the encryption algorithm/key length configured meets the FIPS 140-2/3 validated module requirement specified in the SSP.
+3. Check Group Policy Management Console for the GPO enforcing mandatory drive encryption and confirm it applies to all in-scope OUs.
+4. Review any exception requests for unencrypted media or systems and confirm each has a documented, CCB-approved compensating control.
+5. Document any system found without encryption enabled and open a remediation ticket with the System Administrator.
+6. Export the manage-bde status results and GPO report and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -864,13 +859,12 @@
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. Review IPsec policy and VPN gateway configuration to confirm all remote-access and inter-system transmission paths are encrypted per the SSP-defined cryptographic mechanism.
+2. Verify TLS configuration on internal application/service endpoints enforces the approved minimum protocol version and cipher suite.
+3. Review Splunk VPN/remote-access logs for the period to confirm no sessions were established using disallowed or unencrypted protocols.
+4. Spot-check network captures or device configuration exports on a sample of transmission paths to confirm encryption is actually in effect (not just configured).
+5. Document and remediate any transmission path found using a non-approved or disabled encryption mechanism via a change ticket to the Network Administrator.
+6. Export the IPsec/TLS configuration review and Splunk log excerpt and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -903,13 +897,12 @@
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. Run Get-GPOReport for the GPO enforcing maximum session/re-authentication timeout values and confirm settings match the SSP-defined interval for privilege escalation and role changes.
+2. Query auditpol /get to confirm logon/logoff and special-logon audit subcategories are enabled to capture re-authentication events.
+3. Review Windows Security event log (Event ID 4672/4648/4778) for a sample of privileged sessions to confirm re-authentication was enforced before privilege change or after the idle threshold.
+4. Test re-authentication enforcement on a sample account by triggering a privilege escalation action and confirming a credential prompt occurs per IA-11.
+5. Document and remediate any account or system found bypassing re-authentication via a ticket to the System Administrator.
+6. Export the Get-GPOReport output and Security event log excerpt and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -946,13 +939,12 @@
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. In Splunk, run the boundary/firewall SIEM dashboard to review inbound traffic-volume and connection-rate metrics for anomalies indicating a denial-of-service condition against SC-5 thresholds.
+2. Query Splunk for TLS/session-layer logs to confirm session tokens are being validated and no session-hijacking or spoofing indicators are present per SC-23.
+3. Check the boundary device (firewall/IPS) dashboard for active rate-limiting, SYN-flood protection, or blackhole/sinkhole rules and confirm they remain enabled.
+4. Review any Splunk-triggered DoS or session-anomaly alerts from the shift and confirm each was acknowledged and dispositioned by the Network Administrator.
+5. If an anomaly or alert required action, verify the mitigating control (rate limit, ACL change, session reset) was applied and logged.
+6. Export the Splunk dashboard/alert review as a PDF or CSV and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -985,13 +977,12 @@
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. In Splunk, query the environmental-monitoring data source (building management system/BMS feed) for the server room to pull temperature and humidity readings for the current shift.
+2. Compare logged readings against the facility's documented PE-14 thresholds (e.g., temperature and relative humidity operating range) and flag any out-of-range excursions.
+3. If an alarm fired in the BMS/Splunk dashboard, confirm Facility Security Officer response and corrective action (e.g., HVAC service ticket) was logged.
+4. Physically inspect the space's HVAC readout or sensor display to cross-check against the Splunk-reported values for sensor accuracy.
+5. Note any sensor malfunction or maintenance need and open a facilities work order if required.
+6. Export the environmental dashboard reading and any alarm/ticket record, and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1022,7 +1013,16 @@
       <c r="D14" s="3" t="inlineStr"/>
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>1. Confirm the privacy incident response plan and intake channel (privacy incident mailbox/hotline logged in the GRC/ticketing system) are active and monitored per SE-2.
+2. Pull the ticketing system's open/closed privacy-incident case list for the review period and confirm each case has an assigned Privacy Officer/IR Team Lead and a documented disposition.
+3. For any open privacy incident, verify required notifications (Information Owner/Steward, affected individuals if applicable, ISSM) were sent within the plan's required timeframe.
+4. Verify breach-response actions (containment, harm assessment, notification determination) are documented in the case record per the privacy incident response plan.
+5. Confirm the case tracking log ties each incident to any related accounting-of-disclosures or records-retention entries as required.
+6. Export the case list/ticket export and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
+        </is>
+      </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Responsible: Privacy Officer, IR Team Lead
@@ -1055,7 +1055,16 @@
       </c>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>1. In Splunk, monitor the security-incident correlation dashboard/SIEM alert queue continuously for indicators requiring incident handling under IR-4.
+2. For each triggered alert, verify the CND Team logged a ticket in the incident-tracking system with classification, containment, eradication, and recovery actions per the incident response plan.
+3. Run the Splunk incident-monitoring saved search to confirm all open incidents are being tracked to closure and no alert aged past the SLA without action, per IR-5.
+4. Cross-check the incident ticket count and status against the Splunk alert count for the same period to confirm no alerts were dropped or missed.
+5. Confirm ISSM was notified of any incident meeting reportable-incident criteria.
+6. Export the Splunk incident dashboard and ticketing system status report and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
+        </is>
+      </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Responsible: IR Team Lead / CND Team
@@ -1086,13 +1095,12 @@
       <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current accounting-of-disclosures log from the records-management/AD-integrated tracking system for all disclosures of personal information made outside the organization during the period, per AR-8.
+2. Cross-reference each logged disclosure against the source authorization (data-sharing agreement, need-to-know approval, or legal request) on file.
+3. Verify the log captures the required elements: date, nature, purpose of disclosure, and recipient identity for each entry.
+4. Confirm no disclosures were made without a corresponding log entry by sampling recent Active Directory/system access-export events against the disclosure log.
+5. Address any gaps by adding missing entries and documenting the correction with Privacy Officer sign-off.
+6. Export the reconciled accounting-of-disclosures log and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1125,12 +1133,12 @@
       <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Pattern C — Update / Patch / Signature Refresh
-1. Query the authoritative source (vendor/DISA/NVD advisory feed mirrored locally, or the local update-management tool) for the current required version/signature/key state.
-2. Compare the authoritative current state against the deployed state.
-3. Apply the update through the organization's change-control process (per `execution-plan/ROLE-CROSSWALK.md`'s CCB routing where the update is configuration-relevant).
-4. Verify the update took effect (re-query deployed state).
-5. Log cycle completion (date, prior version, new version, verifier) in the repository location specified in the Task Index.</t>
+          <t>1. In the ePO console, open the DAT/engine signature-version dashboard and confirm all managed endpoints report the current-day DAT file and engine version per SI-3.
+2. Run the ePO Asset/Software Inventory report to identify any endpoints that failed to check in or update within the last Agent Wake-Up cycle.
+3. For non-compliant endpoints, force an Agent Wake-Up call and re-verify signature update completion.
+4. Review the ePO Threat Event Log for the last 24 hours for any malware detections that were not automatically remediated and confirm analyst follow-up.
+5. Check the ePO Policy Compliance query results to confirm on-access scanning remains enabled organization-wide.
+6. Export the ePO DAT compliance dashboard and Threat Event Log summary and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1161,7 +1169,16 @@
       <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="3" t="inlineStr"/>
       <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>1. For the active incident ticket in the incident-tracking system, confirm the IR Team Lead posted a status update per the reporting cadence defined in the incident response plan, per IR-6.
+2. In Splunk, verify the incident's supporting detection data (alert timeline, affected hosts/accounts) is attached or linked to the ticket for the current update.
+3. Confirm the update was distributed to ISSM and, where the incident meets escalation criteria, to AO/DAO and CISO.
+4. Verify the ticket status field (e.g., contained, eradicated, recovering, closed) was updated to reflect current incident state.
+5. Confirm any required external reporting (e.g., US-CERT/DoD CIO per timeline) was submitted if applicable to this incident.
+6. Export the incident status update and distribution record and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
+        </is>
+      </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Responsible: IR Team Lead
@@ -1192,12 +1209,12 @@
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Pattern C — Update / Patch / Signature Refresh
-1. Query the authoritative source (vendor/DISA/NVD advisory feed mirrored locally, or the local update-management tool) for the current required version/signature/key state.
-2. Compare the authoritative current state against the deployed state.
-3. Apply the update through the organization's change-control process (per `execution-plan/ROLE-CROSSWALK.md`'s CCB routing where the update is configuration-relevant).
-4. Verify the update took effect (re-query deployed state).
-5. Log cycle completion (date, prior version, new version, verifier) in the repository location specified in the Task Index.</t>
+          <t>1. Upon notification of a termination, transfer, or need-to-know change, confirm Personnel Security logged the event with a timestamp in the personnel tracking system, per AC-2.
+2. Verify the System Administrator received the notification and, using Active Directory (Get-ADUser), disabled or modified the affected account within the 8-24 hour window required.
+3. Run repadmin /replsummary or check AD replication status to confirm the account change replicated to all domain controllers within the window.
+4. Cross-check the AD account status against the personnel system record to confirm account state matches the personnel action (disabled for termination, group membership updated for transfer/need-to-know change).
+5. Document the elapsed time between notification and account action to confirm the SLA was met.
+6. Export the AD account change log (Get-ADUser query output or Event Viewer account-management events) and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1230,12 +1247,12 @@
       <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Pattern C — Update / Patch / Signature Refresh
-1. Query the authoritative source (vendor/DISA/NVD advisory feed mirrored locally, or the local update-management tool) for the current required version/signature/key state.
-2. Compare the authoritative current state against the deployed state.
-3. Apply the update through the organization's change-control process (per `execution-plan/ROLE-CROSSWALK.md`'s CCB routing where the update is configuration-relevant).
-4. Verify the update took effect (re-query deployed state).
-5. Log cycle completion (date, prior version, new version, verifier) in the repository location specified in the Task Index.</t>
+          <t>1. Upon notification of personnel termination, verify Personnel Security Officer initiated the termination checklist in the personnel/HR system per PS-4.
+2. Confirm the System Administrator revoked the individual's Active Directory account (Get-ADUser -Filter, Disable-ADAccount) and removed group memberships (Get-ADGroupMember) within 24 hours.
+3. Confirm badge/facility access credentials were deactivated by pulling the badge-access system's deactivation log for the individual.
+4. Verify collection of government property, security debrief, and return of any cryptographic/authentication tokens is documented on the termination checklist.
+5. Cross-check the timestamp of account disablement against the termination effective date/time to confirm the 24-hour requirement was met.
+6. Export the completed termination checklist and AD account-disablement log and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1268,12 +1285,12 @@
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Pattern C — Update / Patch / Signature Refresh
-1. Query the authoritative source (vendor/DISA/NVD advisory feed mirrored locally, or the local update-management tool) for the current required version/signature/key state.
-2. Compare the authoritative current state against the deployed state.
-3. Apply the update through the organization's change-control process (per `execution-plan/ROLE-CROSSWALK.md`'s CCB routing where the update is configuration-relevant).
-4. Verify the update took effect (re-query deployed state).
-5. Log cycle completion (date, prior version, new version, verifier) in the repository location specified in the Task Index.</t>
+          <t>1. Upon notification of a personnel transfer, verify Personnel Security Officer initiated the transfer reassessment checklist per PS-5.
+2. Using Get-ADUser and Get-ADGroupMember, confirm the individual's Active Directory group memberships and access rights were reassessed against the gaining position's need-to-know and reassigned/removed as appropriate within 24 hours.
+3. Confirm access to systems, shares, or SCI/SAP compartments tied to the prior position that are no longer required were revoked, and any new access was granted only after gaining-position validation.
+4. Cross-check facility/badge-access permissions were updated to reflect the new duty location or area via the badge-access system.
+5. Verify the timestamp of the AD access change against the transfer effective date to confirm the 24-hour requirement was met.
+6. Export the completed transfer reassessment checklist and AD group-membership change log and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1306,13 +1323,12 @@
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. Run dcdiag /test:frsevent and repadmin /replsummary on all domain controllers to confirm Windows Time service (W32Time) is running and NTP sync is healthy.
+2. Execute w32tm /query /status /verbose on each domain controller and a sample of member servers to capture current time source, stratum, and last-sync offset.
+3. Run a Splunk saved search against the Windows Security/System event log source for Event ID 36 (time provider) and Event ID 129/142 (time service) errors over the review period.
+4. Confirm the authoritative time source (e.g., GPS appliance or external NTP) is correctly configured on the PDC emulator via w32tm /query /configuration.
+5. Flag and remediate any host with clock drift exceeding the JSIG-allowed threshold, re-running w32tm /resync as needed.
+6. Export the Splunk search results and w32tm status output and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -1345,13 +1361,12 @@
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Run the Splunk saved search against the Windows Security event log index covering the review week, filtering for Event IDs 4624/4625 (logon), 4720/4726 (account changes), 4732/4756 (privileged group changes), and 4688 (process creation).
+2. Review the Splunk audit-review dashboard for any triggered correlation alerts and triage each as benign, expected, or requiring escalation.
+3. Cross-check flagged anomalies (e.g., after-hours privileged logons, repeated failed authentications) against the current access roster via Get-ADGroupMember for sensitive groups.
+4. Document findings and dispositions for each flagged event in the weekly audit review log, noting analyst name and resolution.
+5. Escalate any unresolved or suspicious findings to the ISSM per the incident-handling procedure.
+6. Export the Splunk search results and disposition log and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -1384,13 +1399,12 @@
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. Open the ePO console and pull the Threat Event Log filtered to the review week to confirm on-demand and on-access scans completed on all managed endpoints.
+2. Run the ePO Policy Compliance query to identify any endpoints that missed their scheduled scan or show a non-compliant scan policy.
+3. Check the ePO DAT/engine version dashboard to confirm all endpoints are reporting the current signature set as of the scan date.
+4. Investigate and remediate any endpoint shown as non-compliant or with a stale DAT, using ePO Agent Wake-Up to force an immediate scan/update.
+5. Review any detections logged in the Threat Event Log during the period and confirm each was quarantined/cleaned with no unresolved threats remaining.
+6. Export the ePO Threat Event Log and Policy Compliance report and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1423,13 +1437,12 @@
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. Confirm the scheduled weekly-full and daily-incremental backup jobs completed successfully in the backup tool's job history/console for all in-scope systems.
+2. Review the backup job logs for failure, warning, or skipped-file entries and note the affected system and cause for any anomaly.
+3. Verify backup job configuration (retention, encryption, destination/offsite copy) still matches the approved backup schedule documented in the Contingency Plan.
+4. Re-run or manually initiate any failed backup job and confirm successful completion before closing out the cycle.
+5. Verify backup media/storage capacity has sufficient headroom for the next scheduled cycle.
+6. Export the backup job completion report and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -1462,13 +1475,12 @@
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current Nessus scan results and Splunk continuous-monitoring dashboard findings for the review period to identify new, recurring, or closed vulnerabilities.
+2. Cross-reference open POA&amp;M line items against the latest Nessus plugin findings to confirm which weaknesses remain unresolved and which have been remediated.
+3. Update each open POA&amp;M entry's status, scheduled completion date, milestones, and resources in the POA&amp;M tracker, adding new entries for newly identified weaknesses.
+4. Close out POA&amp;M entries with remediation evidence (e.g., rescan showing plugin no longer present) attached.
+5. Route the updated POA&amp;M to the ISSM for review and to the AO/DAO for risk-acceptance awareness on any overdue items.
+6. Export the updated POA&amp;M and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1513,13 +1525,12 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current-month Nessus vulnerability scan report and Splunk continuous-monitoring dashboard export covering the system's authorization boundary.
+2. Generate the current CM-8 component inventory export (e.g., via Get-ADComputer plus ePO Asset/Software Inventory report) and reconcile it against the authorization boundary diagram.
+3. Pull the updated POA&amp;M tracker reflecting current open/closed items per the CA-5 review.
+4. Assemble the Nessus report, inventory export, and POA&amp;M into the monthly ConMon package per the format specified in the Continuous Monitoring Strategy.
+5. Route the assembled package to the ISSM for review and endorsement before submission.
+6. Submit the endorsed ConMon package to the AO/DAO and file the submission record and package contents in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -1552,13 +1563,12 @@
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. Launch the scheduled Nessus credentialed scan job (or confirm the automated scheduled job executed) against the full authorized IP/asset range for the month.
+2. Confirm the scan used current plugin/signature definitions and completed without credential-failure or host-unreachable errors in the Nessus scan status log.
+3. Review the Nessus scan report for new critical/high findings and cross-check against WSUS patch deployment status for affected hosts.
+4. Validate a sample of flagged vulnerabilities against actual host configuration to rule out false positives, noting any exceptions.
+5. Feed newly identified unresolved findings into the POA&amp;M tracker per the CA-5 process.
+6. Export the Nessus scan report and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -1591,12 +1601,12 @@
       <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Pattern C — Update / Patch / Signature Refresh
-1. Query the authoritative source (vendor/DISA/NVD advisory feed mirrored locally, or the local update-management tool) for the current required version/signature/key state.
-2. Compare the authoritative current state against the deployed state.
-3. Apply the update through the organization's change-control process (per `execution-plan/ROLE-CROSSWALK.md`'s CCB routing where the update is configuration-relevant).
-4. Verify the update took effect (re-query deployed state).
-5. Log cycle completion (date, prior version, new version, verifier) in the repository location specified in the Task Index.</t>
+          <t>1. Check the Nessus/Tenable feed update log to confirm the plugin/vulnerability signature set auto-updated on schedule prior to the monthly scan window.
+2. If auto-update did not occur, manually trigger a plugin feed update from the Nessus console and verify the new plugin set version and timestamp.
+3. Confirm the updated plugin set includes coverage for any newly published CVEs or DISA STIG audit file revisions relevant to the environment.
+4. Re-validate that the compliance/configuration-audit scan policy references the correct, current STIG audit file version.
+5. Document the plugin feed version and update timestamp confirmed prior to running the next scheduled scan.
+6. Export the plugin update confirmation log and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -1629,12 +1639,12 @@
       <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Pattern C — Update / Patch / Signature Refresh
-1. Query the authoritative source (vendor/DISA/NVD advisory feed mirrored locally, or the local update-management tool) for the current required version/signature/key state.
-2. Compare the authoritative current state against the deployed state.
-3. Apply the update through the organization's change-control process (per `execution-plan/ROLE-CROSSWALK.md`'s CCB routing where the update is configuration-relevant).
-4. Verify the update took effect (re-query deployed state).
-5. Log cycle completion (date, prior version, new version, verifier) in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current Nessus scan report's flaw/patch-related findings (missing-patch plugins) for the review month.
+2. Cross-reference the Nessus findings against the WSUS console's Update Status report to identify hosts pending approved patches or reporting deployment failures.
+3. Verify patch deployment compliance percentage against the JSIG-required remediation timeline for critical/high severity flaws.
+4. Approve and push any pending patches in WSUS for non-compliant hosts, and re-scan affected hosts in Nessus to confirm remediation.
+5. Document any patches that cannot be applied on schedule with justification and add them to the POA&amp;M tracker.
+6. Export the WSUS Update Status report and Nessus rescan results and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -1667,13 +1677,12 @@
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Pattern D — Test / Exercise
-1. Pull the current, approved test plan/procedure for this exercise.
-2. Execute the test plan step by step exactly as written, recording actual results against each expected result in the plan.
-3. Compare aggregate actual results against the plan's overall success criteria.
-4. Draft an after-action report: what worked, what didn't, root cause of any gap.
-5. For any gap identified, open a POA&amp;M entry and assign a remediation owner and date.
-6. File the test plan, execution log, and AAR in the repository location specified in the Task Index; update the plan itself if the test surfaced a procedural error in it.</t>
+          <t>1. Select a sample of backup sets (full and incremental) from the past month per the backup testing schedule in the Contingency Plan.
+2. Perform a test restoration of the sampled backup data to an isolated recovery/test environment using the backup tool's restore wizard.
+3. Verify file/data integrity and completeness of the restored data by comparing checksums or record counts against the source system.
+4. Time the restoration process and compare it against the Recovery Time Objective (RTO) defined in the Contingency Plan.
+5. Document any restoration failures, data corruption, or RTO shortfalls and initiate corrective action with the backup administrator.
+6. Export the restoration test results and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1706,13 +1715,13 @@
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the electronic physical access control system (PACS) badge-swipe log for the SAPF/restricted area covering the review month.
+2. Cross-reference badge-swipe entries against the current Authorized Access List to flag any entries by personnel not on the list.
+3. Review PACS alarm/exception log (forced-door, held-door, propped-door, badge-reader-tamper events) for the same period.
+4. Correlate any after-hours or anomalous access events with approved visit requests or on-call schedules.
+5. Notify the Facility Security Officer of any unresolved discrepancies for follow-up action.
+6. Document findings in the PE-6 monitoring log, noting any incidents opened.
+7. Export the PACS log review summary and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -1745,13 +1754,13 @@
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the visitor register (electronic PACS visitor log or paper visitor log, per site configuration) for the review month.
+2. Verify each entry contains visitor name, organization, clearance/access authorization verification, escort name, and entry/exit timestamps.
+3. Confirm visitor entries requiring a signed non-disclosure or courier authorization have the supporting form on file.
+4. Check that visitor records are retained per the facility's records-retention schedule and have not been purged early.
+5. Reconcile a sample of visitor entries against escort sign-in sheets to confirm continuous escort coverage.
+6. Note any incomplete or missing entries and route to the Facility Security Officer for correction.
+7. Export the visitor records review summary and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -1788,13 +1797,13 @@
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current Authorized Access List (AAL) for each SAPF/restricted area from the facility access-management system.
+2. Pull the current active-personnel roster (indoctrinated/briefed individuals) from the security officer's personnel tracking system.
+3. Compare the AAL against the active-personnel roster to identify individuals who have been debriefed, transferred, or terminated but remain on the AAL.
+4. Query the PACS door-controller configuration to confirm badge permissions match the current AAL for each controlled entry point.
+5. Remove or flag for removal any unauthorized entries and submit access-control system change requests to update badge permissions.
+6. Physically verify access control devices (cipher locks, biometric readers, mantraps) at each entry point are functioning per PE-3 requirements during the inspection walk-through.
+7. Export the reconciled AAL and PACS configuration comparison and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -1827,12 +1836,13 @@
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Pattern H — Governance / Authorization Decision
-1. Receive and log the complete decision package (assessment results, POA&amp;M, supporting artifacts) from the submitting role.
-2. Review the package against the decision's governing criteria (risk tolerance, control effectiveness, residual risk per NIST SP 800-37's accountability model).
-3. Consult required parties per this role's RACI position (see `execution-plan/ROLE-CROSSWALK.md` and `RACI-MATRIX.md`) before finalizing.
-4. Render and document the decision (approve / approve with conditions / deny), with written rationale.
-5. Distribute the decision to all Informed parties per the RACI position and file the decision record in the repository location specified in the role's runbook.</t>
+          <t>1. Pull open change requests from the configuration/ticketing system queued for CCB review this cycle.
+2. Convene the CCB meeting per the charter, with the CCB Chair confirming quorum of designated voting members.
+3. Present each proposed change with its security-impact analysis and testing/rollback plan for CCB discussion.
+4. Record CCB voting decisions (approve, reject, deferred) for each change in the meeting minutes.
+5. Route approved changes to the ISSM for authorization sign-off and update the change's status in the ticketing system.
+6. Notify the AO/DAO of any changes affecting the system's approved security baseline.
+7. Export the signed CCB meeting minutes and decision record and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -1865,13 +1875,13 @@
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Run a Trellix/McAfee ePO Asset/Software Inventory report to pull the current list of managed endpoints and installed software versions.
+2. Run a `Get-ADComputer -Filter * -Properties *` query (or equivalent AD query) to pull the current list of domain-joined system components.
+3. Compare the ePO and AD outputs against the baseline system component inventory record to identify additions, removals, or discrepancies.
+4. Verify components flagged in ePO as unmanaged or not communicating are investigated and either re-enrolled or formally removed from inventory.
+5. Update the authoritative component inventory record with any confirmed additions/removals and note the associated CCB change ticket number for each.
+6. Route inventory updates exceeding baseline scope to the CCB for change-control disposition.
+7. Export the reconciled inventory report and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -1904,13 +1914,13 @@
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current POA&amp;M items from each subordinate system's individual POA&amp;M tracker in the GRC/ticketing repository.
+2. Consolidate open, overdue, and newly closed POA&amp;M items into the organization-level POA&amp;M rollup register.
+3. Verify each open item still has an assigned resource, milestone dates, and interim mitigation status; flag items past their milestone date as overdue.
+4. Recalculate aggregate risk exposure/metrics (e.g., count of overdue items by severity) for the organization-level risk view.
+5. Brief the ISSM and AO/DAO on overdue or high-risk POA&amp;M items requiring escalation or resource reallocation.
+6. Update the Risk Executive Function notification record for items affecting organizational risk posture.
+7. Export the updated organization-level POA&amp;M rollup and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -1943,13 +1953,13 @@
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current authoritative organization-wide information system inventory record from the GRC/documentation repository.
+2. Query each subordinate ISSM/system owner for newly authorized, decommissioned, or reclassified systems since the last update.
+3. Cross-check reported system status against active Authorization to Operate (ATO) records and expiration dates for each system.
+4. Update the inventory record with system name, unique identifier, authorization boundary, ATO status/expiration, and responsible ISSM for each entry.
+5. Flag systems with expired or soon-to-expire ATOs and notify the AO/DAO and Risk Executive Function.
+6. Reconcile the updated inventory count against the last reported figure and document the reason for any variance.
+7. Export the updated organization-wide inventory and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -1986,13 +1996,13 @@
       <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Run a Splunk saved search against VPN/remote-access and jump-server logs to pull all nonlocal (remote) maintenance sessions for the review month.
+2. Verify each session record includes date/time, maintenance personnel identity, systems accessed, and business justification/ticket reference.
+3. Confirm each nonlocal maintenance session was authorized in advance per the maintenance request/change ticket and used an approved encrypted remote-access method (e.g., VPN with MFA).
+4. Check session termination logs to confirm sessions were properly closed and remote-access accounts disabled/expired after completion.
+5. Cross-reference session activity against the Splunk continuous-monitoring dashboard (CA-7) to confirm no unauthorized commands or lateral movement occurred during the session.
+6. Escalate any unauthorized or unlogged nonlocal maintenance session to the ISSM/ISSO for investigation.
+7. Export the Splunk nonlocal-maintenance session report and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -2025,13 +2035,13 @@
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. Physically inspect the media storage area/container (safe, SCIF storage cabinet, or media library) housing classified/sensitive removable media and digital storage devices.
+2. Verify storage containers meet required physical protection standards (GSA-approved security container, combination lock control, container inventory log) per PE-3/MP-4 requirements.
+3. Confirm environmental controls (temperature, humidity, fire suppression) for the media storage room are within specification per facility monitoring records.
+4. Pull the media inventory/control log and reconcile it against physically stored media to confirm no unaccounted-for items.
+5. Run `manage-bde -status` on a sample of removable/BitLocker-protected drives to confirm encryption remains enabled and keys are escrowed per policy.
+6. Note any discrepancies (missing media, uncontrolled access, environmental exceedance) and route to the Facility Security Officer for corrective action.
+7. Export the media storage inspection checklist and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -2064,13 +2074,13 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Run a Splunk saved search/dashboard against systems processing PII to identify access, export, and query events involving privacy-designated data fields for the review month.
+2. Compare identified access/export events against the approved user list authorized for PII access per the Privacy Impact Assessment (PIA).
+3. Review data loss prevention or file-transfer logs for any bulk export of PII to removable media or external destinations.
+4. Cross-check any flagged anomalous access against open incident tickets to confirm privacy incidents were properly reported per breach-notification procedures.
+5. Verify the System of Records Notice (SORN) and PIA remain current for the systems audited and note any needed updates.
+6. Brief the Privacy Officer and Information Owner/Steward on findings and required corrective actions.
+7. Export the Splunk privacy-monitoring report and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -2103,13 +2113,12 @@
       <c r="F42" s="3" t="inlineStr"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current PII inventory/system-of-records worksheet from the Privacy GRC repository and the prior month's version for comparison.
+2. Query the Information Owner/Steward and System Administrator for any new, modified, or retired data collections, forms, or system holdings containing PII since the last update.
+3. Cross-check any newly onboarded applications or data feeds in the system inventory against the PII holdings list to confirm none were missed.
+4. Update the PII inventory entries (data elements, authority to collect, storage location, retention period) to reflect confirmed changes.
+5. Route the updated inventory to the Privacy Officer for review and sign-off.
+6. File the signed, dated inventory update in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -2142,13 +2151,12 @@
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. In the ePO console, run the Agent Wake-Up/communication status report to confirm all managed endpoints checked in and executed scheduled self-tests within the cycle.
+2. Review the ePO Threat Event Log and Policy Compliance queries for any endpoints reporting failed or disabled security-function self-tests (AV engine, firewall, HIPS).
+3. Cross-reference any Nessus credentialed scan results flagging disabled or non-functional security agents on scanned hosts.
+4. Run a Splunk saved search against Windows Security event log for Service Control Manager events indicating unexpected stopping of security services.
+5. For any host with a failed or missing self-test result, open a remediation ticket and verify the agent is restarted/reinstalled and re-checks in.
+6. Export the ePO compliance summary and Splunk search results, and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -2181,13 +2189,12 @@
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. In ePO, generate the Software/Asset Inventory report and compare current DAT/engine and application version hashes against the last approved baseline.
+2. Run a Tenable Nessus compliance/configuration-audit scan using the applicable file-integrity or software-inventory audit policy against production hosts.
+3. Review the scan results and ePO Policy Compliance dashboard for unauthorized binary changes, unsigned executables, or firmware version drift from the approved baseline.
+4. For any discrepancy, validate against the CM baseline/change record to confirm whether the change was authorized; open a CCB ticket for unauthorized changes.
+5. Document confirmed integrity violations and remediation actions taken (rollback, reimage, re-baseline).
+6. Export the Nessus and ePO reports and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -2220,12 +2227,12 @@
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>Pattern C — Update / Patch / Signature Refresh
-1. Query the authoritative source (vendor/DISA/NVD advisory feed mirrored locally, or the local update-management tool) for the current required version/signature/key state.
-2. Compare the authoritative current state against the deployed state.
-3. Apply the update through the organization's change-control process (per `execution-plan/ROLE-CROSSWALK.md`'s CCB routing where the update is configuration-relevant).
-4. Verify the update took effect (re-query deployed state).
-5. Log cycle completion (date, prior version, new version, verifier) in the repository location specified in the Task Index.</t>
+          <t>1. Run a Tenable Nessus credentialed vulnerability scan against all in-scope hosts to identify missing security patches published in the last 30 days.
+2. Cross-reference the scan's plugin-based findings export against the vendor patch/advisory list and the ePO DAT/engine signature-version dashboard to confirm current update levels.
+3. Verify WSUS/patch management console shows required security updates approved and deployed to the applicable computer groups.
+4. For any host missing a required update past the remediation window, open a POA&amp;M or remediation ticket with target completion date.
+5. Re-scan remediated hosts with Nessus to confirm the missing-patch findings have cleared.
+6. Export the before/after Nessus plugin findings and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -2258,13 +2265,12 @@
       <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current-period metrics extract from the GRC/ticketing repository (e.g., patch compliance rate, POA&amp;M closure rate, incident count, scan finding aging).
+2. Compute each performance measure against its defined threshold/target as specified in the security metrics plan.
+3. Draft the information security performance measures report summarizing trends, threshold breaches, and root causes for the period.
+4. Route the draft report to the ISSM for accuracy review and to the AO/DAO for briefing.
+5. Brief the Risk Executive Function on measures that breached thresholds and any resulting risk-acceptance or remediation decisions.
+6. File the finalized performance measures report in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -2297,13 +2303,12 @@
       <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Run Get-ADGroupMember against each privileged AD group (Domain Admins, Enterprise Admins, and system-specific privileged roles) to export the current membership list.
+2. Compare the exported membership against the last-approved privileged access roster and current user account listing from Get-ADUser.
+3. Validate each privileged account against its supporting access authorization/justification record and confirm the account holder still requires that role.
+4. Identify and remove/disable any privileged accounts belonging to separated, transferred, or no-longer-justified personnel using Active Directory Users and Computers or the corresponding PowerShell cmdlet.
+5. Document justification for retained privileged accounts and any removals performed.
+6. Export the reconciled privileged account list and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -2340,13 +2345,12 @@
       <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Run Get-ADGroupMember and Get-ADUser -Properties MemberOf against accounts holding elevated or security-function privileges (e.g., audit log management, security policy administration) to export current assignments.
+2. Review each assignment against the account holder's current job function and the least-privilege justification on file to confirm continued need.
+3. Check GPMC/Get-GPOReport for User Rights Assignment settings (e.g., Manage auditing and security log, Debug programs) to confirm only authorized accounts hold sensitive rights.
+4. For any account no longer requiring elevated or security-function access, submit a CCB access-change request and remove the assignment via Active Directory.
+5. Have the ISSM countersign the reassessed privileged/security-function access list.
+6. Export the updated access assignment report and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -2379,13 +2383,12 @@
       <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. In ePO, generate the current Software/Asset Inventory report across all managed endpoints.
+2. Compare the inventory against the CCB-approved authorized software whitelist/baseline document.
+3. Check Group Policy-enforced AppLocker or Software Restriction Policy rules via GPMC/Get-GPOReport to confirm the technical whitelist matches the approved list.
+4. Flag any unauthorized, unapproved, or unlicensed software detected on endpoints and open a CCB ticket for disposition (approve retroactively, remove, or exception).
+5. Coordinate removal of unauthorized software or update of the whitelist/AppLocker policy based on CCB decision.
+6. Export the reconciled software inventory and CCB disposition record, and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -2418,13 +2421,12 @@
       <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the change/release log from the CCB tracking system for all changes implemented in production during the quarter.
+2. Run Get-ADGroupMember against groups granting production/operational deployment or administrative privileges to export the current holder list.
+3. Cross-check each privileged account holder against active change tickets to confirm the access is still tied to an open or recurring authorized change role, not a stale one-time grant.
+4. Revoke or downgrade production/operational privileges for accounts whose associated change work has closed, using Active Directory account management.
+5. Document the reassessment outcome and any access revocations in the CCB record.
+6. Export the updated privileged-access-to-change mapping and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -2457,13 +2459,12 @@
       <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current hardware/software asset inventory from the CM repository, including vendor, version, and support-status fields.
+2. Cross-reference each component's vendor end-of-life/end-of-support (EOL/EOS) notices and lifecycle roadmaps to identify components that have reached or are approaching EOS.
+3. For each unsupported component found, verify whether a documented risk acceptance, extended support contract, or replacement/upgrade plan is on file.
+4. For components lacking mitigation, open a POA&amp;M item specifying compensating controls (isolation, enhanced monitoring) or a decommission/upgrade timeline.
+5. Brief the ISSM and AO/DAO on newly identified unsupported components and proposed dispositions.
+6. Export the updated unsupported-components list and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
@@ -2496,13 +2497,12 @@
       <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current System Security Plan (SSP) data-at-rest control implementation statement and the list of systems/media in scope (servers, workstations, removable media, databases).
+2. On Windows hosts, run manage-bde -status on each system disk to confirm BitLocker is enabled with the approved encryption method (XTS-AES 256) and protector configuration.
+3. For database or application-level encryption, query the DBMS configuration (e.g. Transparent Data Encryption status) or file-system encryption settings and record the enabled/disabled state per instance.
+4. Cross-check any exceptions or systems reporting non-compliant encryption status against open Plan of Action and Milestones (POA&amp;M) entries to confirm they are tracked.
+5. Document any newly discovered unencrypted asset as a finding and open a POA&amp;M or remediation ticket with a target date.
+6. Compile the per-system encryption status into a compliance summary and file it in the repository location specified in the Task Index with the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -2535,13 +2535,12 @@
       <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Identify all data transmission paths in scope (site-to-site VPN, remote access VPN, internal encrypted tunnels, web services) from the current network architecture diagram.
+2. Review IPsec policy configuration in Windows Defender Firewall with Advanced Security (or the VPN concentrator's config export) to confirm approved cipher suites (e.g. AES-256, SHA-2) are enforced for each tunnel.
+3. Pull TLS configuration/certificate details for internal web services and confirm only approved protocol versions and cipher suites are enabled (e.g. via a Nessus SSL/TLS configuration scan).
+4. Review Splunk VPN/remote-access logs for any connections negotiated with a deprecated or unapproved cipher and flag them as findings.
+5. Verify certificates used for transmission encryption are current (not expired) and issued by an approved CA.
+6. Record findings, remediate or open a POA&amp;M for any non-compliant path, and file the summary report in the repository location specified in the Task Index with the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
@@ -2572,7 +2571,16 @@
       <c r="D54" s="3" t="inlineStr"/>
       <c r="E54" s="3" t="inlineStr"/>
       <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="3" t="inlineStr"/>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>1. Pull the current-quarter security and privacy awareness reminder content package (phishing indicators, incident reporting procedure, insider threat indicators, privacy handling reminders) from the training repository.
+2. Confirm the content reflects any changes to policy, threat landscape, or reporting procedures since the prior quarter and update the material accordingly.
+3. Distribute the reminder via the organizational LMS or email distribution list to all cleared personnel/system users in scope.
+4. Export the LMS distribution/read-receipt or delivery-confirmation roster to confirm which personnel received the reminder.
+5. Follow up with personnel who did not acknowledge receipt and document the escalation.
+6. File the distributed content, the delivery roster, and the distribution date in the repository location specified in the Task Index alongside the Training Manager's name.</t>
+        </is>
+      </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
           <t>Responsible: Training Manager
@@ -2607,13 +2615,12 @@
       <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Export the current remote-access authorized-user list via Get-ADGroupMember on the designated remote-access security group(s) and compare it against the VPN/RAS server's active session and authorization configuration.
+2. Export the current wireless-access authorized-device/user list from the wireless controller or NPS (Network Policy Server) RADIUS configuration.
+3. Cross-reference both lists against the current personnel roster and approved access-request tickets to identify any account that should have been removed (terminated, transferred, or expired access).
+4. Remove or disable via Active Directory any remote-access or wireless-access authorization no longer justified, and document the change in a ticket.
+5. Confirm remote-access and wireless-access configurations still enforce required controls (e.g. MFA, encryption) per AC-17/AC-18 requirements.
+6. Export the reconciled authorization lists and file them in the repository location specified in the Task Index alongside the Network Administrator's name and date.</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
@@ -2646,13 +2653,12 @@
       <c r="F56" s="3" t="inlineStr"/>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current inventory of publicly accessible information systems/pages (public-facing web servers, portals, or shared content areas) in scope.
+2. Review the designated content-approval workflow records to confirm all currently published public content has a documented authorization/review sign-off.
+3. Manually inspect the live public-facing content (or use a Nessus/web-content scan) to check for inadvertent exposure of nonpublic, CUI, or classified information.
+4. Remove or request removal of any unauthorized or sensitive content discovered and document the corrective action.
+5. Confirm the personnel authorized to post to the public-facing system are current by cross-checking against Get-ADGroupMember output for the publishing role/group.
+6. File the review findings, corrective actions, and the reviewed content inventory in the repository location specified in the Task Index alongside the ISSO's name and date.</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
@@ -2689,13 +2695,12 @@
       <c r="F57" s="3" t="inlineStr"/>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Export the current firewall/boundary-device rule base (e.g. via Windows Defender Firewall with Advanced Security export or the perimeter firewall's config export) covering access-enforcement and information-flow rules.
+2. Run Get-ADGroupMember and Get-ADUser against the access-control groups referenced in the rule set to confirm rule assignments still map to authorized, active accounts/roles.
+3. Review the rule set for overly permissive entries (e.g. any-any rules, unused legacy rules) and compare against the approved firewall rule justification/change-request records.
+4. Validate flow-enforcement boundaries (e.g. VLAN/security zone segmentation, data-flow labels) against the current network architecture diagram to confirm no unauthorized cross-domain paths exist.
+5. Submit any required rule changes through the CCB change-request process and document the ticket number.
+6. Export the validated rule set and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
@@ -2728,13 +2733,12 @@
       <c r="F58" s="3" t="inlineStr"/>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current inventory of devices requiring identification/authentication (domain-joined workstations, servers, network devices) via Get-ADComputer.
+2. Verify machine-authentication certificates or Kerberos computer-account authentication are correctly configured by reviewing the AD Certificate Services issued-certificate report or running dcdiag to confirm computer-account trust relationships.
+3. Confirm any non-Windows or IoT/network devices use an approved device-authentication mechanism (e.g. 802.1X certificate-based authentication) by checking the NPS/RADIUS authentication logs.
+4. Identify any device account that is stale, disabled, or missing required authentication configuration and remediate (rejoin domain, reissue certificate, or disable the device account).
+5. Spot-check a sample of devices against the device-authentication baseline/STIG requirement to confirm compliance.
+6. Export the device authentication compliance results and file them in the repository location specified in the Task Index alongside the Network Administrator's name and date.</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -2767,13 +2771,12 @@
       <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Run a Tenable Nessus credentialed compliance/configuration-audit scan against the applicable DISA STIG audit file for the in-scope systems.
+2. Export the Tenable scan results report showing pass/fail status per STIG configuration item.
+3. Cross-check any Group Policy-enforced baseline settings using Get-GPOReport or gpresult /h on a sample of systems to confirm the GPO settings match the approved baseline.
+4. Review Trellix/McAfee ePO Policy Compliance queries to confirm endpoint configuration policies are applied and reporting compliant across the managed asset inventory.
+5. For any finding showing configuration drift from baseline, open a remediation ticket and route any proposed baseline change through the CCB for approval.
+6. Export the Nessus and ePO compliance reports and file them in the repository location specified in the Task Index alongside the System Administrator's name and date.</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
@@ -2806,13 +2809,12 @@
       <c r="F60" s="3" t="inlineStr"/>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Review Windows Security event log and Splunk index access-control lists (ACLs) to confirm only authorized ISSO/audit personnel accounts have read/write/delete permission on audit log stores.
+2. Confirm Splunk's index retention and role-based access control configuration prevents modification or deletion of ingested audit data by non-privileged accounts.
+3. Check auditpol /get on source Windows systems to confirm audit-policy and event-log-clearing events are themselves being logged and forwarded to Splunk.
+4. Query Splunk for any Event ID 1102 (audit log cleared) or unauthorized access attempts to the audit log storage/directories and investigate any hits.
+5. Verify backup/archival of audit logs to a separate protected repository is occurring on schedule per the log-management SOP.
+6. Document the access-control and log-integrity verification results and file the report in the repository location specified in the Task Index alongside the ISSO's name and date.</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
@@ -2845,13 +2847,12 @@
       <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Export the current media-access authorization list (personnel authorized to access/use removable media, e.g. via the AD security group governing media-access privileges) using Get-ADGroupMember.
+2. Cross-reference the exported list against the current personnel roster and approved access-request tickets to confirm all listed individuals still require media access and hold current authorization.
+3. Review Trellix/McAfee ePO device-control policy or Windows Group Policy removable-storage restriction settings to confirm technical enforcement matches the approved authorization list.
+4. Remove or update authorization in Active Directory for any individual whose access is no longer justified (e.g. role change, termination) and document the change in a ticket.
+5. Spot-check a sample of recent removable-media usage events (ePO or Windows Event Log) against the authorization list to confirm no unauthorized use occurred.
+6. Export the reconciled media-access authorization list and file it in the repository location specified in the Task Index alongside the ISSO's name and date.</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
@@ -2884,13 +2885,12 @@
       <c r="F62" s="3" t="inlineStr"/>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current media inventory list from the removable-media log/register covering all classified media (CDs/DVDs, USB, external drives, backup tapes) in use during the quarter.
+2. Physically inspect a sample of media in storage/transit to confirm each item bears the required classification banner, control markings, and downgrading/declassification instructions per the SCG.
+3. Verify BitLocker-protected removable drives display the correct classification label via `manage-bde -status` and physical label check.
+4. Cross-check marked classification level on each sampled item against the classification recorded in the media control register/SCI accountability log.
+5. Document any unmarked, mismarked, or unmarked-but-required-exempt media (e.g., media within a closed/secured system per waiver) and issue corrective tasking to the custodian.
+6. Export the sampled inventory checklist with marking findings and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
@@ -2927,13 +2927,12 @@
       <c r="F63" s="3" t="inlineStr"/>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the physical facility diagram identifying all transmission line runs (network cabling, KVM extenders) and output device locations (printers, fax, monitors displaying classified data) within the SCIF/SAPF.
+2. Physically inspect cable runs and junction/patch panels to confirm they are routed through protected/controlled areas or secured in conduit per the PE-4 requirement.
+3. Verify each output device (printer, plotter, display) is located within an area restricted to authorized, cleared personnel and check the AD security group (`Get-ADGroupMember`) controlling access to the room/badge zone.
+4. Confirm printer/output device access is not left unattended by observing during a walk-through and checking print-queue logs for evidence of unclaimed classified output.
+5. Note any exposed cabling, unsecured patch panels, or output devices in uncontrolled space and open a corrective-action ticket with the Facility Security Officer.
+6. Export the walk-through checklist and access-control screenshot and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
@@ -2966,13 +2965,12 @@
       <c r="F64" s="3" t="inlineStr"/>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current PII data inventory/System of Records Notice (SORN) listing all PII data elements collected and their authorized sources.
+2. Sample a set of records from the PII holding (HR system, access-roster database, or equivalent) and validate accuracy, completeness, and currency of key fields (name, SSN, clearance status) against the authoritative source system.
+3. Run any available data-validation or duplicate-detection query/report against the PII holding to identify stale, inconsistent, or orphaned records.
+4. Confirm collection forms/intake processes still restrict input to the minimum necessary PII elements defined in the SORN/Privacy Impact Assessment.
+5. Document identified data-quality discrepancies and route correction/purge actions to the Information Owner/Steward for remediation.
+6. Export the data-quality review findings memo and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
@@ -3005,13 +3003,12 @@
       <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the complaint log/ticketing export from the privacy complaint intake system (or GRC tracker) for all privacy-related complaints received in the quarter.
+2. Categorize each complaint by type (e.g., unauthorized disclosure, inaccurate record, denied access request) and calculate resolution time against the complaint-handling SLA.
+3. Compile trend statistics (volume by category, average time-to-resolve, recurring root causes) into the quarterly privacy complaint trend report.
+4. Compare current-quarter trends against the prior quarter's report to flag any emerging pattern requiring a process or training change.
+5. Brief the trend findings and any recommended corrective actions to the Information Owner/Steward.
+6. Export the trend report and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
@@ -3044,13 +3041,12 @@
       <c r="F66" s="3" t="inlineStr"/>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Export the current firewall/boundary-device rule base (Windows Defender Firewall with Advanced Security GPO or network boundary device ACL export) for the SAP enclave.
+2. Review each rule for business justification, confirming source/destination/port/protocol restrictions still match the approved System Security Plan network diagram.
+3. Run a Splunk query against boundary-device/firewall logs to identify any traffic matching overly permissive rules (e.g., any-any) or rules with zero hit-count over the review period.
+4. Cross-check the rule set against the CCB-approved firewall change log to confirm no undocumented rule additions or modifications occurred.
+5. Flag unused, overly permissive, or undocumented rules and submit a rule-removal/tightening request through the CCB.
+6. Export the rule-set review report and Splunk query results and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -3083,13 +3079,12 @@
       <c r="F67" s="3" t="inlineStr"/>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Open the ePO console and pull the anti-spam/email-gateway module policy compliance report for all managed endpoints/mail relays.
+2. Confirm spam-filter signature/definition versions are current by checking the DAT/engine signature-version dashboard against vendor release dates.
+3. Query the ePO Threat Event Log (or Splunk mail-gateway index) for spam-detection events over the review period and verify quarantine/block actions were correctly applied.
+4. Sample a set of quarantined messages to confirm no false-positive legitimate mail was blocked and no spam reached end-user inboxes undetected.
+5. Run a Nessus compliance scan against the mail relay/gateway configuration to confirm anti-spam settings meet the STIG baseline.
+6. Export the ePO policy compliance report and Splunk query results and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
@@ -3122,13 +3117,12 @@
       <c r="F68" s="3" t="inlineStr"/>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Run `Get-ADUser -Filter * -Properties MemberOf,Enabled,LastLogonDate` (or equivalent GPMC/AD report) to export the current list of all non-privileged user accounts on the system.
+2. Cross-reference each account against the current access roster/personnel clearance list to confirm the user still requires access and holds the appropriate clearance/need-to-know.
+3. Run `Get-ADGroupMember` against standard user groups to confirm no non-privileged account has inadvertently inherited privileged/admin group membership.
+4. Identify accounts with no logon activity for the review period (via `LastLogonDate`) and flag them for disablement per the account-management policy.
+5. Route identified stale, unauthorized, or excess-privilege accounts to the ISSO for disablement/removal action and confirm closure.
+6. Export the account review report and disablement confirmation and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -3161,13 +3155,12 @@
       <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>Pattern D — Test / Exercise
-1. Pull the current, approved test plan/procedure for this exercise.
-2. Execute the test plan step by step exactly as written, recording actual results against each expected result in the plan.
-3. Compare aggregate actual results against the plan's overall success criteria.
-4. Draft an after-action report: what worked, what didn't, root cause of any gap.
-5. For any gap identified, open a POA&amp;M entry and assign a remediation owner and date.
-6. File the test plan, execution log, and AAR in the repository location specified in the Task Index; update the plan itself if the test surfaced a procedural error in it.</t>
+          <t>1. Schedule and conduct a semi-annual incident-response tabletop exercise or functional test using a scenario drawn from the current IR plan.
+2. During the exercise, inject simulated indicators into Splunk (or validate against existing SIEM detection rules) to confirm the IR team can detect, triage, and escalate within the plan's required timelines.
+3. Time and record each phase of the response (detection, containment, eradication, recovery, reporting) against the IR plan's target metrics.
+4. Capture an after-action report documenting exercise participants, scenario, timeline performance, and any gaps in detection or escalation procedures.
+5. Update the IR plan and Splunk detection/alerting rules to address identified gaps and route changes through the ISSM for approval.
+6. Export the after-action report and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
@@ -3200,13 +3193,12 @@
       <c r="F70" s="3" t="inlineStr"/>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Run an ePO Asset/Software Inventory report (or `Get-ADComputer -Filter * -Properties *` for domain-joined systems) to export the current list of all computers and endpoints on the SAP network.
+2. Pull the physical removable-media/hardware accountability log for all classified removable media and portable devices issued to the program.
+3. Reconcile the ePO/AD system inventory and the removable-media log against the CCB-approved hardware baseline list to identify unauthorized, missing, or unaccounted-for items.
+4. Physically spot-check a sample of listed devices/media against their logged location to confirm accountability records are accurate.
+5. Document discrepancies (unauthorized additions, missing items, custody gaps) and route them to the ISSM and CCB for investigation and correction.
+6. Export the reconciled inventory report and file it in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -3239,12 +3231,13 @@
       <c r="F71" s="3" t="inlineStr"/>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>Pattern E — Documentation / Policy Review and Update
-1. Pull the current approved version of the document and its associated control citations/ODPs.
-2. Review the document against current control requirements, current system state, and any changes since the last review (organizational, technical, regulatory).
-3. Draft revisions (or a no-change re-approval memo if none are needed).
-4. Route the draft for required approval per its governing role (CCB for configuration-relevant plans; ISSM/AO/DAO per the document's own sign-off requirement).
-5. Publish the new version and archive the superseded version per its retention requirement.</t>
+          <t>1. Pull the current approved baseline configuration document (hardware/software/GPO baseline) from the CM repository for the system.
+2. Run an ePO Asset/Software Inventory report to capture the as-built software/version inventory across all managed endpoints.
+3. Run `Get-GPOReport` (GPMC XML/HTML export) to capture the as-applied Group Policy configuration and compare it against the documented baseline GPO settings.
+4. Identify deltas between the as-built/as-applied state and the documented baseline (unauthorized software, drifted GPO settings, unpatched configuration items).
+5. Draft baseline configuration updates or remediation actions for identified drift and submit them through the CCB for review and approval.
+6. Publish the updated baseline document upon CCB approval and archive the prior version per version-control procedure.
+7. Export the comparison report and CCB approval record and file them in the repository location specified in the Task Index alongside the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
@@ -3277,12 +3270,13 @@
       <c r="F72" s="3" t="inlineStr"/>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>Pattern E — Documentation / Policy Review and Update
-1. Pull the current approved version of the document and its associated control citations/ODPs.
-2. Review the document against current control requirements, current system state, and any changes since the last review (organizational, technical, regulatory).
-3. Draft revisions (or a no-change re-approval memo if none are needed).
-4. Route the draft for required approval per its governing role (CCB for configuration-relevant plans; ISSM/AO/DAO per the document's own sign-off requirement).
-5. Publish the new version and archive the superseded version per its retention requirement.</t>
+          <t>1. Pull the current-version policy document for each of the 17 family -1 controls (AC-1, AT-1, AU-1, CA-1, CM-1, CP-1, IA-1, IR-1, MA-1, MP-1, PE-1, PL-1, PS-1, RA-1, SA-1, SC-1, SI-1) from the organizational policy repository (GRC document library / SharePoint policy library).
+2. Compare each policy's stated procedures against the current NIST SP 800-53 Rev.4 (JSIG-tailored) control text and against any organizational, mission, or regulatory changes since the last approval date recorded in the document's revision history.
+3. For each family, draft redlined revisions to the policy/procedure document, or if no substantive changes are needed, draft a one-page no-change re-approval memo citing the review date and reviewer.
+4. Route each drafted policy revision or no-change memo through the Configuration Control Board (CCB) for technical review, then to the ISSM for content sign-off.
+5. Obtain final approval signature from the AO/DAO (or designated approval authority per the policy's governance block) for each of the 17 documents.
+6. Publish the approved/re-approved versions to the policy repository, incrementing version numbers and superseding prior copies.
+7. File the signed approval memos/CCB routing records and updated policy set in the compliance repository location specified in the Task Index, annotated with the ISSM's name and approval date.</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -3315,12 +3309,13 @@
       <c r="F73" s="3" t="inlineStr"/>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Pattern E — Documentation / Policy Review and Update
-1. Pull the current approved version of the document and its associated control citations/ODPs.
-2. Review the document against current control requirements, current system state, and any changes since the last review (organizational, technical, regulatory).
-3. Draft revisions (or a no-change re-approval memo if none are needed).
-4. Route the draft for required approval per its governing role (CCB for configuration-relevant plans; ISSM/AO/DAO per the document's own sign-off requirement).
-5. Publish the new version and archive the superseded version per its retention requirement.</t>
+          <t>1. Retrieve the current signed Contingency Plan (CP) document from the compliance/GRC document repository and note its last-approved revision date.
+2. Review the plan's recovery procedures, alternate processing/storage site details, and system component inventory against the current Windows Server environment, including any changes to backup targets, failover hosts, or recovery-point/recovery-time objectives.
+3. Cross-check the plan's system inventory and dependencies against current Get-ADComputer output and the backup job configuration in the Windows Server backup console to confirm no drift.
+4. Draft revisions to the CP addressing any identified gaps (e.g., changed IP schemes, decommissioned servers, new applications), or draft a no-change re-approval memo if the annual review finds the plan still accurate.
+5. Route the updated CP through the ISSM for review and the AO/DAO for approval signature.
+6. Publish the approved CP to the document repository, superseding the prior version, and notify system administrators of any procedural changes.
+7. File the signed approval record and updated CP in the repository location specified in the Task Index with the ISSM's name and approval date.</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
@@ -3353,13 +3348,13 @@
       <c r="F74" s="3" t="inlineStr"/>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>Pattern D — Test / Exercise
-1. Pull the current, approved test plan/procedure for this exercise.
-2. Execute the test plan step by step exactly as written, recording actual results against each expected result in the plan.
-3. Compare aggregate actual results against the plan's overall success criteria.
-4. Draft an after-action report: what worked, what didn't, root cause of any gap.
-5. For any gap identified, open a POA&amp;M entry and assign a remediation owner and date.
-6. File the test plan, execution log, and AAR in the repository location specified in the Task Index; update the plan itself if the test surfaced a procedural error in it.</t>
+          <t>1. Schedule and conduct the annual contingency plan exercise (tabletop walkthrough or functional recovery test) per the test plan defined in the current Contingency Plan.
+2. Execute the defined recovery procedure against a test/non-production target, restoring a representative server or dataset from the Windows Server Backup / recovery tooling to verify the documented recovery steps and RTO/RPO are achievable.
+3. Record test participants, start/end times, each procedural step executed, and any deviations or failures encountered during the exercise.
+4. Identify corrective actions for any step that failed or exceeded the target recovery time, and log them as findings with assigned owners and due dates.
+5. Update the Contingency Plan to reflect lessons learned and corrected procedures based on the test results.
+6. Brief the ISSM and ISSO on test outcomes and obtain ISSM sign-off on the after-action report.
+7. File the signed after-action report, test log, and any CP updates in the repository location specified in the Task Index with the test date and ISSM's name.</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
@@ -3392,13 +3387,13 @@
       <c r="F75" s="3" t="inlineStr"/>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>Pattern D — Test / Exercise
-1. Pull the current, approved test plan/procedure for this exercise.
-2. Execute the test plan step by step exactly as written, recording actual results against each expected result in the plan.
-3. Compare aggregate actual results against the plan's overall success criteria.
-4. Draft an after-action report: what worked, what didn't, root cause of any gap.
-5. For any gap identified, open a POA&amp;M entry and assign a remediation owner and date.
-6. File the test plan, execution log, and AAR in the repository location specified in the Task Index; update the plan itself if the test surfaced a procedural error in it.</t>
+          <t>1. Develop or update the Security Assessment Plan identifying the controls in scope for this cycle's independent assessment, consistent with the system's control baseline.
+2. Execute a credentialed Tenable Nessus vulnerability/compliance scan against the in-scope hosts using the appropriate DISA STIG audit file, and export the scan results report.
+3. Conduct manual control assessment procedures (interview, examine, test) for controls not verifiable via automated scanning, documenting evidence for each control's Assessment Objective.
+4. Cross-reference Splunk continuous-monitoring dashboards for relevant log-based evidence (e.g., audit logging, account management activity) supporting the controls under review.
+5. Document assessment results, findings, and residual risk in a Security Assessment Report (SAR), assigning a satisfied/not-satisfied determination per control.
+6. Deliver the SAR to the ISSM and AO/DAO with any recommended Plan of Action and Milestones (POA&amp;M) entries for unsatisfied controls.
+7. File the signed SAR, supporting Nessus scan exports, and POA&amp;M updates in the repository location specified in the Task Index with the SCA's name and assessment date.</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
@@ -3431,13 +3426,13 @@
       <c r="F76" s="3" t="inlineStr"/>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>Pattern D — Test / Exercise
-1. Pull the current, approved test plan/procedure for this exercise.
-2. Execute the test plan step by step exactly as written, recording actual results against each expected result in the plan.
-3. Compare aggregate actual results against the plan's overall success criteria.
-4. Draft an after-action report: what worked, what didn't, root cause of any gap.
-5. For any gap identified, open a POA&amp;M entry and assign a remediation owner and date.
-6. File the test plan, execution log, and AAR in the repository location specified in the Task Index; update the plan itself if the test surfaced a procedural error in it.</t>
+          <t>1. Define the penetration test scope, rules of engagement, and authorized test window, and obtain AO/DAO written authorization prior to testing.
+2. Execute external and internal penetration testing against in-scope systems, using Tenable Nessus scan results as the vulnerability baseline to prioritize exploitation attempts.
+3. Attempt exploitation of identified vulnerabilities and privilege-escalation/lateral-movement paths, documenting each successful and attempted technique with timestamps.
+4. Correlate testing activity against Splunk logs (Windows Security event log, firewall/boundary-device logs) to validate detection and alerting coverage during the test.
+5. Compile a penetration test report detailing findings, exploited vulnerabilities, risk ratings, and recommended remediations.
+6. Brief the ISSM and SCA on findings and open POA&amp;M entries for any critical or high-risk findings requiring remediation.
+7. File the signed penetration test report and POA&amp;M updates in the repository location specified in the Task Index with the SCA/SCAR's name and test date.</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
@@ -3470,13 +3465,13 @@
       <c r="F77" s="3" t="inlineStr"/>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current list of maintenance tools authorized for use on the system (physical and software-based diagnostic/repair tools) from the maintenance tool inventory log or GRC asset repository.
+2. Physically and/or electronically inspect each listed maintenance tool for unauthorized modification, unapproved software additions, or missing digital signatures/checksums where applicable.
+3. Verify that any media associated with maintenance tools (e.g., diagnostic USB drives, boot disks) has been scanned for malicious code prior to use, per the media protection procedure.
+4. Cross-check the maintenance tool inventory against current system administrator records to identify any tools in use that are not on the approved list, and remove or quarantine unapproved tools.
+5. Update the approved maintenance tool list to add newly approved tools or retire decommissioned ones, with justification for each change.
+6. Route the updated tool list through the ISSM for review and approval.
+7. File the signed approved maintenance tool list and inspection notes in the repository location specified in the Task Index with the System Administrator's name and review date.</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
@@ -3509,12 +3504,13 @@
       <c r="F78" s="3" t="inlineStr"/>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>Pattern E — Documentation / Policy Review and Update
-1. Pull the current approved version of the document and its associated control citations/ODPs.
-2. Review the document against current control requirements, current system state, and any changes since the last review (organizational, technical, regulatory).
-3. Draft revisions (or a no-change re-approval memo if none are needed).
-4. Route the draft for required approval per its governing role (CCB for configuration-relevant plans; ISSM/AO/DAO per the document's own sign-off requirement).
-5. Publish the new version and archive the superseded version per its retention requirement.</t>
+          <t>1. Pull the current organizational Risk Assessment Report and prior POA&amp;M from the GRC repository to establish the baseline of previously identified risks.
+2. Run a current credentialed Tenable Nessus vulnerability scan across the system's asset inventory and export the findings report, including CVSS scores and plugin details.
+3. Review the past year's incident records, audit findings, and any newly introduced hardware/software/network changes for new threat sources or vulnerabilities not captured in the prior assessment.
+4. Reassess likelihood and impact ratings for each identified risk using the current scan data and threat information, updating the risk register accordingly.
+5. Update the Risk Assessment Report narrative and risk register with new/closed risks, and reconcile against open POA&amp;M items.
+6. Route the updated Risk Assessment Report through the ISSM for review, with SCA consultation, and obtain AO/DAO acknowledgment.
+7. File the signed updated Risk Assessment Report and supporting Nessus export in the repository location specified in the Task Index with the ISSM's name and review date.</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
@@ -3547,13 +3543,13 @@
       <c r="F79" s="3" t="inlineStr"/>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current roster of cleared personnel with system access from Active Directory (Get-ADUser scoped to privileged/access groups via Get-ADGroupMember) and cross-reference against the personnel security access-agreement file.
+2. Identify personnel whose signed Access Agreement (e.g., Acceptable Use Policy / Non-Disclosure Agreement) is more than one year old or has never been executed.
+3. Distribute the current-version Access Agreement to each identified individual for review and re-signature, using the organization's personnel security tracking system.
+4. Collect and verify completed, signed agreements, confirming signature dates and version acknowledged match the current approved agreement text.
+5. Update the personnel security tracking system/records to reflect the new signature date for each individual, and flag any non-responders for account suspension per policy.
+6. Notify the ISSM of personnel who failed to re-sign within the grace period so access can be restricted in Active Directory.
+7. File the collected signed access agreements and the updated tracking roster in the repository location specified in the Task Index with the Personnel Security Officer's name and completion date.</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
@@ -3586,13 +3582,13 @@
       <c r="F80" s="3" t="inlineStr"/>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>Pattern F — Training Delivery
-1. Confirm the current-cycle training content is up to date against policy/threat landscape changes since the last delivery.
-2. Identify the full population required to complete this training cycle.
-3. Schedule and deliver the training to the identified population.
-4. Record completion status for every individual on the roster.
-5. Follow up on every incomplete/non-completion with the individual's supervisor or the Personnel Security function; document the follow-up.
-6. File the completion roster in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current roster of all personnel with system access from the organization's LMS/training-tracking system and cross-reference against the Active Directory active-account list to identify who requires the annual refresher.
+2. Deploy the current-version security awareness refresher training module (covering current threat trends, phishing, insider-threat indicators, and policy updates) to all identified personnel via the LMS.
+3. Monitor LMS completion status throughout the training window and issue reminder notices to personnel with overdue completions.
+4. Export the LMS completion roster showing completion date and pass status for each individual at the close of the training window.
+5. Identify personnel who failed to complete training by the deadline and notify the ISSM/ISSO for access-restriction action per policy.
+6. Reconcile the completion roster against the Active Directory access list to confirm no active account holder is missing a current-year completion record.
+7. File the exported LMS completion roster in the repository location specified in the Task Index with the Training Manager's name and reporting date.</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
@@ -3625,13 +3621,13 @@
       <c r="F81" s="3" t="inlineStr"/>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>Pattern F — Training Delivery
-1. Confirm the current-cycle training content is up to date against policy/threat landscape changes since the last delivery.
-2. Identify the full population required to complete this training cycle.
-3. Schedule and deliver the training to the identified population.
-4. Record completion status for every individual on the roster.
-5. Follow up on every incomplete/non-completion with the individual's supervisor or the Personnel Security function; document the follow-up.
-6. File the completion roster in the repository location specified in the Task Index.</t>
+          <t>1. Identify all personnel in role-based positions requiring specialized training (e.g., system administrators, ISSOs, privileged users) by cross-referencing job role/duty assignments against the Active Directory privileged-group membership (Get-ADGroupMember).
+2. Assign the current-version role-based training module(s) applicable to each identified role in the organization's LMS/training-tracking system.
+3. Track and follow up on module completion for each assigned individual throughout the designated training period, issuing reminders for overdue personnel.
+4. Export the LMS completion roster showing role, module completed, completion date, and pass status for each assigned individual.
+5. Identify personnel who did not complete role-based training by the deadline and notify the ISSM/ISSO to consider restricting elevated access pending completion.
+6. Reconcile the role-based completion roster against the privileged-account list to confirm every privileged-role holder has a current-cycle completion record.
+7. File the exported role-based training completion roster in the repository location specified in the Task Index with the Training Manager's name and reporting date.</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
@@ -3664,13 +3660,12 @@
       <c r="F82" s="3" t="inlineStr"/>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Pattern F — Training Delivery
-1. Confirm the current-cycle training content is up to date against policy/threat landscape changes since the last delivery.
-2. Identify the full population required to complete this training cycle.
-3. Schedule and deliver the training to the identified population.
-4. Record completion status for every individual on the roster.
-5. Follow up on every incomplete/non-completion with the individual's supervisor or the Personnel Security function; document the follow-up.
-6. File the completion roster in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current-year incident response training curriculum from the LMS and confirm it reflects the latest IR plan version and lessons-learned from the past year's incidents.
+2. Cross-reference the LMS enrollment roster against the list of personnel with incident-handling roles (IR team, help desk, ISSO staff) to identify who is due for the annual refresher.
+3. Schedule and deliver the refresher session (live or LMS-hosted module), including tabletop-style incident scenarios relevant to the system.
+4. Export the LMS completion roster showing course name, completion date, and pass/fail status for each required attendee.
+5. Follow up individually with any personnel showing incomplete or overdue status and re-assign the module with a new due date.
+6. File the completion roster and session materials in the training records repository with the Training Manager's name and sign-off date.</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
@@ -3703,13 +3698,12 @@
       <c r="F83" s="3" t="inlineStr"/>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>Pattern F — Training Delivery
-1. Confirm the current-cycle training content is up to date against policy/threat landscape changes since the last delivery.
-2. Identify the full population required to complete this training cycle.
-3. Schedule and deliver the training to the identified population.
-4. Record completion status for every individual on the roster.
-5. Follow up on every incomplete/non-completion with the individual's supervisor or the Personnel Security function; document the follow-up.
-6. File the completion roster in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current contingency plan (CP) and most recent backup/recovery test results from the Windows Server backup/recovery tooling to identify any procedural changes since the last training cycle.
+2. Cross-reference the LMS enrollment roster against personnel assigned contingency roles (system administrators, backup operators, alternate-site staff) to identify who is due for the annual refresher.
+3. Deliver the contingency training, including a walkthrough of current backup/restore procedures and any updated recovery-time/recovery-point objectives.
+4. Incorporate at least one hands-on or simulated recovery exercise (e.g., a sample manage-bde/backup restore walkthrough) so trainees demonstrate familiarity with the actual recovery tooling.
+5. Export the LMS completion roster showing course name, completion date, and pass/fail status for each required attendee.
+6. File the completion roster and training materials in the training records repository with the Training Manager's name and sign-off date.</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
@@ -3742,12 +3736,13 @@
       <c r="F84" s="3" t="inlineStr"/>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>Pattern E — Documentation / Policy Review and Update
-1. Pull the current approved version of the document and its associated control citations/ODPs.
-2. Review the document against current control requirements, current system state, and any changes since the last review (organizational, technical, regulatory).
-3. Draft revisions (or a no-change re-approval memo if none are needed).
-4. Route the draft for required approval per its governing role (CCB for configuration-relevant plans; ISSM/AO/DAO per the document's own sign-off requirement).
-5. Publish the new version and archive the superseded version per its retention requirement.</t>
+          <t>1. Pull the current Incident Response Plan (IRP) document and compare it against the incident types and alert categories currently configured in Splunk's incident-detection saved searches/correlation rules.
+2. Review Splunk's incident/case history for the past cycle to identify any incident types, escalation paths, or notification gaps not currently addressed in the IRP.
+3. Confirm IRP contact lists, escalation chain, and external reporting requirements (e.g., US-CERT/JSIG reporting timelines) are current.
+4. Draft plan revisions reflecting any organizational, technical, or Splunk detection-capability changes, or a no-change re-approval memo if none are needed.
+5. Route the revised or re-approved IRP through the ISSM for review and the AO/DAO for approval.
+6. Publish the approved IRP to the documentation repository and notify the IR team and CISO of the update.
+7. File the approved plan and approval memo in the repository location specified in the Task Index with the ISSM's name and approval date.</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
@@ -3780,12 +3775,13 @@
       <c r="F85" s="3" t="inlineStr"/>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>Pattern E — Documentation / Policy Review and Update
-1. Pull the current approved version of the document and its associated control citations/ODPs.
-2. Review the document against current control requirements, current system state, and any changes since the last review (organizational, technical, regulatory).
-3. Draft revisions (or a no-change re-approval memo if none are needed).
-4. Route the draft for required approval per its governing role (CCB for configuration-relevant plans; ISSM/AO/DAO per the document's own sign-off requirement).
-5. Publish the new version and archive the superseded version per its retention requirement.</t>
+          <t>1. Export the current list of audited event categories/IDs from the Windows Security event log configuration (auditpol /get /category:*) on representative systems.
+2. Compare the exported audit policy against the auditable-events list currently ingested and indexed by Splunk to confirm all required event types are being collected.
+3. Review recent Splunk incident and audit findings to identify any event types that should be added to or removed from the auditable-events list based on operational need.
+4. Update the auditable-events list document to reflect any additions, removals, or reclassifications, noting the rationale for each change.
+5. Apply corresponding auditpol / Group Policy audit-policy changes via GPMC where the list update requires new event categories to be enabled.
+6. Route the updated list through the ISSM/ISSO for review and approval.
+7. File the approved auditable-events list in the repository with the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
@@ -3818,13 +3814,13 @@
       <c r="F86" s="3" t="inlineStr"/>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Run Get-ADComputer/GPMC baseline reports to pull the current Group Policy-enforced service and port configuration for domain systems.
+2. Generate a Trellix/McAfee ePO Software/Asset Inventory report to identify all installed applications and running services across managed endpoints.
+3. Compare both outputs against the system's approved ports/protocols/services (PPS) baseline in the CCB-approved configuration document to identify unauthorized or unnecessary functions.
+4. Disable or remove any identified unnecessary services, ports, or protocols via Group Policy or ePO policy enforcement, or submit a CCB exception request if a business need exists.
+5. Document findings and remediation actions in a PPS review report, including before/after counts of disabled items.
+6. Route the report through the CCB for review and the ISSM for approval.
+7. File the signed report in the repository location specified in the Task Index with the System Administrator's name and date.</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
@@ -3857,12 +3853,13 @@
       <c r="F87" s="3" t="inlineStr"/>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>Pattern C — Update / Patch / Signature Refresh
-1. Query the authoritative source (vendor/DISA/NVD advisory feed mirrored locally, or the local update-management tool) for the current required version/signature/key state.
-2. Compare the authoritative current state against the deployed state.
-3. Apply the update through the organization's change-control process (per `execution-plan/ROLE-CROSSWALK.md`'s CCB routing where the update is configuration-relevant).
-4. Verify the update took effect (re-query deployed state).
-5. Log cycle completion (date, prior version, new version, verifier) in the repository location specified in the Task Index.</t>
+          <t>1. Pull the physical access device inventory (badge readers, cipher locks, keyed locks, safes) from the facility access-control system or badge log export.
+2. Physically inspect each secure space/entry point and reconcile the observed devices and lock hardware against the inventory list, noting discrepancies.
+3. Change combinations on cipher locks/safes and re-key or reissue keys for keyed entry points per the facility's periodic rotation schedule.
+4. Update the Active Directory-integrated physical access control system (or badge system) to revoke/reissue electronic credentials tied to changed hardware.
+5. Photograph or log evidence of completed combination/key changes (e.g., lock-change work orders, key-issue log signatures).
+6. Route the updated inventory and rotation log to the PSO for review and sign-off.
+7. File the inventory, rotation log, and PSO sign-off in the repository location specified in the Task Index with the Facility Security Officer's name and date.</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
@@ -3895,12 +3892,13 @@
       <c r="F88" s="3" t="inlineStr"/>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>Pattern E — Documentation / Policy Review and Update
-1. Pull the current approved version of the document and its associated control citations/ODPs.
-2. Review the document against current control requirements, current system state, and any changes since the last review (organizational, technical, regulatory).
-3. Draft revisions (or a no-change re-approval memo if none are needed).
-4. Route the draft for required approval per its governing role (CCB for configuration-relevant plans; ISSM/AO/DAO per the document's own sign-off requirement).
-5. Publish the new version and archive the superseded version per its retention requirement.</t>
+          <t>1. Pull the current System Security Plan (SSP) from the GRC/documentation repository and compare its control implementation statements against the current authorization boundary, system architecture diagrams, and POA&amp;M items.
+2. Interview or coordinate with system owners and ISSOs to identify any hardware, software, network, or mission changes since the last SSP update.
+3. Update control implementation descriptions, system boundary diagrams, and interconnection details in the SSP to reflect current state, or draft a no-change re-approval memo if the system is unchanged.
+4. Reconcile the SSP's control baseline against the latest JSIG/NIST SP 800-53 Rev.4 tailoring guidance to confirm no applicable controls are missing.
+5. Route the updated SSP through the ISSO for technical review and the AO/DAO for formal approval/re-authorization.
+6. Publish the approved SSP version to the GRC repository, superseding the prior version.
+7. File the approved SSP and approval record in the repository location specified in the Task Index with the ISSM's name and date.</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
@@ -3933,13 +3931,13 @@
       <c r="F89" s="3" t="inlineStr"/>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current Rules of Behavior (RoB) document from the GRC/documentation repository and confirm it reflects current acceptable-use, remote-access, and removable-media requirements.
+2. Export the roster of all active system users (e.g., via Get-ADUser against the authorized user group) requiring a signed RoB acknowledgment.
+3. Cross-reference the user roster against the signed-acknowledgment tracking log (LMS or GRC repository) to identify personnel with missing, expired, or superseded acknowledgments.
+4. Issue the current RoB for signature/acknowledgment to any personnel with missing or outdated acknowledgments, via the LMS or a documented signature process.
+5. Follow up on outstanding acknowledgments until 100% of active users have a current signed record on file.
+6. Route a summary compliance report to the ISSM for review.
+7. File the updated acknowledgment log and compliance report in the repository location specified in the Task Index with the ISSO's name and date.</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
@@ -3972,13 +3970,13 @@
       <c r="F90" s="3" t="inlineStr"/>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current inventory of external information system service providers (cloud services, MSPs, telecom carriers, cross-domain solution providers) from the GRC/documentation repository.
+2. For each provider, review the current contract, Interconnection Security Agreement (ISA), or Service Level Agreement (SLA) to confirm required security controls and JSIG/NIST SP 800-53 obligations are still specified and current.
+3. Request and review each provider's most recent compliance evidence (e.g., FedRAMP authorization package, SOC 2 report, or equivalent attestation) to confirm continued compliance.
+4. Identify any providers with expired agreements, lapsed authorizations, or unresolved compliance gaps and initiate remediation or re-negotiation actions.
+5. Update the external service provider inventory and compliance status log with findings.
+6. Route the compliance summary to the ISSM for review and the AO/DAO for awareness.
+7. File the updated inventory and compliance summary in the repository location specified in the Task Index with the ISSM's name and date.</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
@@ -4015,12 +4013,13 @@
       <c r="F91" s="3" t="inlineStr"/>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>Pattern C — Update / Patch / Signature Refresh
-1. Query the authoritative source (vendor/DISA/NVD advisory feed mirrored locally, or the local update-management tool) for the current required version/signature/key state.
-2. Compare the authoritative current state against the deployed state.
-3. Apply the update through the organization's change-control process (per `execution-plan/ROLE-CROSSWALK.md`'s CCB routing where the update is configuration-relevant).
-4. Verify the update took effect (re-query deployed state).
-5. Log cycle completion (date, prior version, new version, verifier) in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current cryptographic key inventory (PKI certificates, VPN pre-shared keys/IPsec keys, BitLocker recovery keys, disk/data encryption keys) from the key management log in the GRC/documentation repository.
+2. Identify all keys approaching or past their scheduled rotation/expiration date per the organization's key management plan.
+3. Generate/rotate expiring keys and certificates using the applicable mechanism (e.g., PKI reissuance, IPsec policy update in Windows Defender Firewall with Advanced Security, manage-bde key rotation for BitLocker volumes) and confirm the corresponding cryptographic protection configuration (e.g., approved FIPS-validated algorithms) remains unchanged.
+4. Securely retire and destroy or archive superseded keys per the key management plan's disposal procedures.
+5. Update the key inventory log with new key identifiers, issuance dates, and expiration dates.
+6. Route the updated key inventory to the ISSM/ISSO for review.
+7. File the updated key inventory and rotation record in the repository location specified in the Task Index with the System Administrator's name and date.</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
@@ -4053,12 +4052,13 @@
       <c r="F92" s="3" t="inlineStr"/>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>Pattern E — Documentation / Policy Review and Update
-1. Pull the current approved version of the document and its associated control citations/ODPs.
-2. Review the document against current control requirements, current system state, and any changes since the last review (organizational, technical, regulatory).
-3. Draft revisions (or a no-change re-approval memo if none are needed).
-4. Route the draft for required approval per its governing role (CCB for configuration-relevant plans; ISSM/AO/DAO per the document's own sign-off requirement).
-5. Publish the new version and archive the superseded version per its retention requirement.</t>
+          <t>1. Pull the current system security categorization (FIPS 199 / CNSSI 1253 confidentiality-integrity-availability impact levels) from the SSP and the SAP-specific overlay.
+2. Run a current Nessus credentialed scan of the enclave and compare identified asset types, data flows, and mission-critical hosts against the categorization assumptions on record.
+3. Cross-check with the ISSM and SCA whether any mission change, new interconnection, or data-type addition (e.g., new intelligence compartment) has occurred since the last categorization.
+4. Determine whether the impact levels for C, I, and A still match actual system usage and threat exposure; flag any discrepancy for re-categorization.
+5. If no change is warranted, draft a no-change memo signed by the ISSM; if a change is warranted, draft the revised categorization statement for AO/DAO adjudication.
+6. Route the categorization statement (or no-change memo) through the SCA for concurrence and the AO/DAO for approval signature.
+7. File the signed categorization statement/memo and the supporting Nessus asset report in the security authorization repository per the Task Index, with reviewer name and date.</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
@@ -4091,13 +4091,12 @@
       <c r="F93" s="3" t="inlineStr"/>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current position risk designation roster from the personnel security/HR system, listing each billet's designated sensitivity/risk level (e.g., IT-I/II/III, Special-Sensitive, Critical-Sensitive).
+2. Cross-reference each position against its current duties, system access level, and required investigation tier (T3, T5, T5R) to confirm the designation still matches actual responsibilities.
+3. Identify any position that has changed scope (e.g., gained privileged system access or SAP indoctrination duties) without a corresponding designation update.
+4. Coordinate with the ISSM to confirm designations align with the access each billet holds in the system access control list.
+5. Update the position risk designation records for any billet requiring reclassification and route through the Personnel Security Officer for signature.
+6. File the signed, current-year position risk designation roster in the personnel security records repository per the Task Index, with reviewer name and date.</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
@@ -4130,12 +4129,12 @@
       <c r="F94" s="3" t="inlineStr"/>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>Pattern E — Documentation / Policy Review and Update
-1. Pull the current approved version of the document and its associated control citations/ODPs.
-2. Review the document against current control requirements, current system state, and any changes since the last review (organizational, technical, regulatory).
-3. Draft revisions (or a no-change re-approval memo if none are needed).
-4. Route the draft for required approval per its governing role (CCB for configuration-relevant plans; ISSM/AO/DAO per the document's own sign-off requirement).
-5. Publish the new version and archive the superseded version per its retention requirement.</t>
+          <t>1. Pull the current Privacy Impact Assessment (PIA) on file for the system from the privacy documentation repository.
+2. Compare the PIA's data-collection, use, and sharing descriptions against the current SSP data flow diagrams and any new PII-processing functionality added since the last PIA cycle.
+3. Interview the Information Owner/Steward to identify any new or discontinued PII collection points, storage locations, or third-party disclosures.
+4. Update the PIA sections affected (data elements collected, purpose, retention, access controls, sharing arrangements) or draft a no-change certification memo if no material change occurred.
+5. Route the updated PIA (or no-change certification) through the ISSM for security-control concurrence and the Information Owner/Steward for signature.
+6. Publish the approved PIA update and file it in the privacy program repository per the Task Index, with reviewer name and date.</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
@@ -4168,13 +4167,12 @@
       <c r="F95" s="3" t="inlineStr"/>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current PII inventory/data holdings list documenting each category of PII the system collects, stores, or processes.
+2. For each PII data element, verify against current mission/business need whether the element is still required or could be reduced, masked, tokenized, or eliminated.
+3. Consult with the Data Owner and ISSM on any proposed minimization changes (e.g., truncating SSNs to last-4, purging obsolete fields, shortening retention of raw PII).
+4. Document minimization findings, including elements recommended for reduction or removal and the business justification for any PII retained in full.
+5. Route the minimization review findings through the Information Owner/Steward for decision and, where system changes are needed, submit a change request to the CCB.
+6. File the completed PII minimization review report in the privacy program repository per the Task Index, with reviewer name and date.</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
@@ -4211,12 +4209,12 @@
       <c r="F96" s="3" t="inlineStr"/>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>Pattern E — Documentation / Policy Review and Update
-1. Pull the current approved version of the document and its associated control citations/ODPs.
-2. Review the document against current control requirements, current system state, and any changes since the last review (organizational, technical, regulatory).
-3. Draft revisions (or a no-change re-approval memo if none are needed).
-4. Route the draft for required approval per its governing role (CCB for configuration-relevant plans; ISSM/AO/DAO per the document's own sign-off requirement).
-5. Publish the new version and archive the superseded version per its retention requirement.</t>
+          <t>1. Pull all current privacy notices, System of Records Notices (SORNs), and Privacy Act statements applicable to the system from the privacy documentation repository and the Federal Register SORN listing.
+2. Verify each notice/statement's routine uses, authority citations, and data categories still match the system's actual PII collection and processing as described in the current PIA.
+3. Confirm SORNs remain published and unexpired in the Federal Register; identify any requiring republication due to system or use changes.
+4. Draft updated notice/statement/SORN language for any identified discrepancy, or a no-change certification memo if all remain accurate.
+5. Route drafted updates through the Privacy Officer and Information Owner/Steward for approval, and submit any SORN revision through the agency's Federal Register publication process.
+6. File the current, approved notices/statements/SORNs (or no-change memo) in the privacy program repository per the Task Index, with reviewer name and date.</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
@@ -4253,13 +4251,12 @@
       <c r="F97" s="3" t="inlineStr"/>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current list of internal users/business units and external third parties (contractors, agencies, cross-program partners) with authorized access to system information.
+2. Review data-sharing agreements, MOUs/MOAs, and interconnection security agreements (ISAs) on file for each third party to confirm they remain current and cover the actual data being shared.
+3. Compare actual observed information flows (e.g., recent data transfer/export logs or access requests) against what is authorized under the internal-use policy and each sharing agreement.
+4. Flag any sharing arrangement lacking a current signed agreement, or any internal use exceeding the documented purpose, for corrective action.
+5. Coordinate with the ISSM and Information Owner/Steward to remediate gaps (terminate unauthorized sharing, execute/renew agreements as needed).
+6. File the compliance review findings and any updated/executed agreements in the privacy program repository per the Task Index, with reviewer name and date.</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
@@ -4292,12 +4289,13 @@
       <c r="F98" s="3" t="inlineStr"/>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>Pattern E — Documentation / Policy Review and Update
-1. Pull the current approved version of the document and its associated control citations/ODPs.
-2. Review the document against current control requirements, current system state, and any changes since the last review (organizational, technical, regulatory).
-3. Draft revisions (or a no-change re-approval memo if none are needed).
-4. Route the draft for required approval per its governing role (CCB for configuration-relevant plans; ISSM/AO/DAO per the document's own sign-off requirement).
-5. Publish the new version and archive the superseded version per its retention requirement.</t>
+          <t>1. Pull the current signed Configuration Management Plan (CMP) from the configuration management repository.
+2. Compare the CMP's documented baseline definitions, CM roles, and change workflow against the actual current AD Group Policy baseline configuration exported via `Get-GPOReport` and the Trellix ePO software inventory report.
+3. Confirm the CMP's listed CCB membership, meeting cadence, and change-approval thresholds still reflect current program staffing and practice.
+4. Identify any gap between documented CM procedures and actual practice (e.g., undocumented approved software, baseline drift) and note required plan updates.
+5. Draft CMP revisions addressing identified gaps, or a no-change re-approval memo if the plan remains accurate.
+6. Route the CMP update/re-approval memo through the CCB for review and the ISSM for signature.
+7. Publish the approved CMP and file it in the configuration management repository per the Task Index, with reviewer name and date.</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
@@ -4330,13 +4328,13 @@
       <c r="F99" s="3" t="inlineStr"/>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>Pattern D — Test / Exercise
-1. Pull the current, approved test plan/procedure for this exercise.
-2. Execute the test plan step by step exactly as written, recording actual results against each expected result in the plan.
-3. Compare aggregate actual results against the plan's overall success criteria.
-4. Draft an after-action report: what worked, what didn't, root cause of any gap.
-5. For any gap identified, open a POA&amp;M entry and assign a remediation owner and date.
-6. File the test plan, execution log, and AAR in the repository location specified in the Task Index; update the plan itself if the test surfaced a procedural error in it.</t>
+          <t>1. Schedule and execute a system recovery/reconstitution test using the current backup set, restoring the system (or a designated test instance) from the most recent Windows Server backup image.
+2. Validate post-restoration system integrity by running `dcdiag` and `repadmin /replsummary` (for AD-dependent systems) and confirming application/service functionality against baseline.
+3. Time the recovery process and compare actual recovery time/recovery point against the RTO/RPO targets specified in the Contingency Plan.
+4. Document any deviations, failures, or manual workarounds encountered during the restoration test.
+5. Update the Contingency Plan and recovery procedures to reflect lessons learned and correct any deficiencies identified during the test.
+6. Route the test results and any Contingency Plan updates through the ISSM for review and ISSO for concurrence.
+7. File the recovery test report, including timestamps, restored-system validation output, and sign-off, in the contingency planning repository per the Task Index, with reviewer name and date.</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
@@ -4377,13 +4375,12 @@
       <c r="F100" s="3" t="inlineStr"/>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current Contingency Plan sections identifying the designated alternate storage site, alternate processing site, and primary/alternate telecommunications service providers.
+2. Contact or coordinate a site-readiness check with the alternate storage/processing site to confirm current operational status, physical/environmental safeguards, and data currency of replicated backups.
+3. Verify with the Network Administrator that alternate telecommunications circuits (e.g., backup ISP/carrier links) are provisioned, tested, and free of shared single points of failure with the primary site.
+4. Confirm service agreements/contracts for the alternate site and telecom services remain active and cover the required capacity and priority-of-service provisions.
+5. Document any deficiency (e.g., lapsed contract, untested failover circuit, insufficient distance from primary site) and route corrective actions through the ISSM.
+6. File the alternate-site and telecom readiness verification report in the contingency planning repository per the Task Index, with reviewer name and date.</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
@@ -4416,13 +4413,13 @@
       <c r="F101" s="3" t="inlineStr"/>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the facility's current TEMPEST/emanations security (EMSEC) assessment or countermeasures review approved for the SAPF from the physical security records repository.
+2. Physically inspect the SAPF perimeter, RF shielding, filtered power/signal lines, and equipment placement (e.g., red/black separation) for compliance with the site's approved TEMPEST countermeasures plan.
+3. Verify inspection/test zone (ITZ) boundaries and any required TEMPEST test measurements are current and within the certification validity period; coordinate with the Certified TEMPEST Technical Authority (CTTA) if recertification is due.
+4. Photograph any observed deviations (e.g., unshielded penetrations, unauthorized equipment relocation) for the inspection record.
+5. Coordinate with the ISSM to confirm no new IT equipment or cabling introduced since the last review has created an information leakage pathway.
+6. Document findings and route any required remediation or CTTA recertification request through the Facility Security Officer to the PSO for approval.
+7. File the TEMPEST/information-leakage inspection report and photographs in the physical security records repository per the Task Index, with reviewer name and date.</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
@@ -4459,13 +4456,12 @@
       <c r="F102" s="3" t="inlineStr"/>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>Pattern D — Test / Exercise
-1. Pull the current, approved test plan/procedure for this exercise.
-2. Execute the test plan step by step exactly as written, recording actual results against each expected result in the plan.
-3. Compare aggregate actual results against the plan's overall success criteria.
-4. Draft an after-action report: what worked, what didn't, root cause of any gap.
-5. For any gap identified, open a POA&amp;M entry and assign a remediation owner and date.
-6. File the test plan, execution log, and AAR in the repository location specified in the Task Index; update the plan itself if the test surfaced a procedural error in it.</t>
+          <t>1. Physically inspect all fire detection and suppression equipment (smoke/heat detectors, pull stations, fire extinguishers, sprinkler or clean-agent suppression systems) in the SCIF/facility and record inspection tags and last-service dates.
+2. Coordinate with the fire alarm monitoring vendor or building engineering to trigger a functional test of the detection and suppression system and confirm the alarm signal reaches the monitoring station.
+3. Inspect the space for water-damage risk factors (overhead plumbing, sprinkler heads above sensitive equipment, roof leaks, raised-floor moisture) and photograph any deficiencies found.
+4. Verify extinguisher inspection tags and suppression system service records are current against the facility's fire protection service contract schedule.
+5. Document any deficiencies (failed detector, expired extinguisher, active leak) as findings and open a corrective action ticket with a remediation deadline.
+6. Complete the fire protection/water damage inspection checklist, obtain FSO sign-off, and file it in the facility security records repository with the inspector's name and date per the Task Index.</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
@@ -4498,13 +4494,12 @@
       <c r="F103" s="3" t="inlineStr"/>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current roster of active third-party/contractor personnel with facility or system access from the Personnel Security Officer's tracking system or GRC repository.
+2. Cross-check each contractor's file for a current, signed Non-Disclosure Agreement and verify the applicable contract/task order includes the required personnel security clause (DD Form 254 or equivalent).
+3. Confirm each contractor's investigation/clearance level and adjudication status is current by checking JPAS/DISS records against the access roster.
+4. Verify contractor security training completion (initial and annual refresher) via the training LMS completion roster.
+5. Flag any contractor with an expired clearance, missing NDA, or lapsed training and initiate access suspension or remediation with the sponsoring contract office.
+6. Document the review results in a compliance memo, obtain PSO sign-off, and file it in the personnel security records repository with the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
@@ -4537,11 +4532,12 @@
       <c r="F104" s="3" t="inlineStr"/>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>Pattern G — Retention / Disposal
-1. Identify all records that have passed their retention window per the applicable schedule (NARA, organizational records schedule, or the specific window cited in this task's Control ID(s)).
-2. Verify no candidate record is under legal hold, active investigation, or open POA&amp;M/incident reference.
-3. Execute disposal (secure deletion or destruction per the record's classification/handling requirement) for all cleared candidates.
-4. Log the disposal action (what, when, method, authorizer) in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current Splunk audit log retention/archival policy configuration for indexes ingesting Windows Security event log and other audit sources and confirm the configured retention period meets or exceeds the applicable NARA records schedule (6-7 years).
+2. Run a Splunk search against the archive/frozen bucket index to confirm audit records from the oldest required retention year are still retrievable and have not been prematurely purged.
+3. Verify offline/cold storage media (tape, WORM, or archive storage) holding audit records beyond Splunk's hot/warm retention window is indexed and retrievable, and spot-check one archived record set for integrity.
+4. Cross-reference the Splunk frozenTimePeriodInSecs and archival job schedule against the organization's NARA-approved records disposition schedule to confirm no gap exists.
+5. Identify any audit record sets that have reached the end of the retention period and route them for authorized disposition per the records schedule.
+6. Document the retention verification results, including Splunk configuration screenshots and sample retrieval evidence, and file them in the audit records repository with the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
@@ -4574,11 +4570,12 @@
       <c r="F105" s="3" t="inlineStr"/>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>Pattern G — Retention / Disposal
-1. Identify all records that have passed their retention window per the applicable schedule (NARA, organizational records schedule, or the specific window cited in this task's Control ID(s)).
-2. Verify no candidate record is under legal hold, active investigation, or open POA&amp;M/incident reference.
-3. Execute disposal (secure deletion or destruction per the record's classification/handling requirement) for all cleared candidates.
-4. Log the disposal action (what, when, method, authorizer) in the repository location specified in the Task Index.</t>
+          <t>1. Run Get-ADUser and Get-ADComputer with a filter on Deleted/Disabled and LastLogonDate against the domain to pull all identifiers (usernames, SIDs, computer accounts) retired within the current cycle.
+2. Query the AD Recycle Bin or tombstone reuse history to confirm no retired username or SID has been reassigned to a new user or system within 2 years of retirement.
+3. Review the account provisioning process/naming convention documentation to confirm new-account creation procedures block reuse of any identifier within the 2-year window (e.g., unique suffixing, permanent disable rather than delete).
+4. Spot-check a sample of newly created accounts against the retired-identifier list to confirm none collide with an identifier retired in the last 2 years.
+5. Document any violation of the reuse restriction as a finding and open a remediation ticket with the System Administrator.
+6. Export the AD query results and reuse-verification findings, and file them in the identity management records repository with the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
@@ -4611,11 +4608,12 @@
       <c r="F106" s="3" t="inlineStr"/>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>Pattern G — Retention / Disposal
-1. Identify all records that have passed their retention window per the applicable schedule (NARA, organizational records schedule, or the specific window cited in this task's Control ID(s)).
-2. Verify no candidate record is under legal hold, active investigation, or open POA&amp;M/incident reference.
-3. Execute disposal (secure deletion or destruction per the record's classification/handling requirement) for all cleared candidates.
-4. Log the disposal action (what, when, method, authorizer) in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current control assessment tracking matrix (POA&amp;M/assessment schedule) from the GRC repository listing every control in the system security plan and its last assessment date.
+2. Cross-reference the matrix against the 3-year assessment cycle requirement to identify any control not assessed via a Nessus scan, manual review, or interview within the past 3 years.
+3. Run or pull the most recent Nessus credentialed/compliance scan results and Splunk continuous-monitoring dashboard exports to confirm technical controls have current assessment evidence.
+4. For controls lacking recent technical scan coverage (e.g., PS, PE, MP families), confirm an assessor interview, document review, or physical inspection was conducted and recorded within the cycle.
+5. Flag any control past its 3-year assessment window and schedule it with the SCA/SCAR for immediate assessment.
+6. Update the control assessment tracking matrix with the current cycle's completion dates, obtain SCA sign-off, and file it in the assessment records repository with the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
@@ -4648,11 +4646,12 @@
       <c r="F107" s="3" t="inlineStr"/>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>Pattern G — Retention / Disposal
-1. Identify all records that have passed their retention window per the applicable schedule (NARA, organizational records schedule, or the specific window cited in this task's Control ID(s)).
-2. Verify no candidate record is under legal hold, active investigation, or open POA&amp;M/incident reference.
-3. Execute disposal (secure deletion or destruction per the record's classification/handling requirement) for all cleared candidates.
-4. Log the disposal action (what, when, method, authorizer) in the repository location specified in the Task Index.</t>
+          <t>1. Pull the incident-response ticketing/case management system's (or Splunk ES incident review) configured record retention and archival policy for closed incident cases.
+2. Confirm the retention clock for each closed incident is calculated from the date all follow-up/corrective actions were completed, not the incident close date, by spot-checking case metadata fields.
+3. Query the incident record repository for any case approaching or past the 3-year post-follow-up retention threshold and verify it has not been purged prematurely.
+4. Cross-check the system's automated purge/archival job logs against the records-management policy to confirm no incident record was deleted before its retention threshold was reached.
+5. Archive incident records that have reached the 3-year threshold to long-term storage per the organization's records-management policy, and confirm archived records remain retrievable.
+6. Document the retention verification results (record counts, oldest retained case, any purge-log discrepancies), obtain ISSM sign-off, and file the report in the incident response records repository with the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr">
@@ -4685,11 +4684,12 @@
       <c r="F108" s="3" t="inlineStr"/>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>Pattern G — Retention / Disposal
-1. Identify all records that have passed their retention window per the applicable schedule (NARA, organizational records schedule, or the specific window cited in this task's Control ID(s)).
-2. Verify no candidate record is under legal hold, active investigation, or open POA&amp;M/incident reference.
-3. Execute disposal (secure deletion or destruction per the record's classification/handling requirement) for all cleared candidates.
-4. Log the disposal action (what, when, method, authorizer) in the repository location specified in the Task Index.</t>
+          <t>1. Pull the visitor access control log (physical sign-in register or electronic badge-access system export) for the facility covering the applicable retention window.
+2. Verify the visitor log capture fields (name, organization, sponsor, date/time in-out, escort) are complete for the sampled period.
+3. Confirm the retention period configured in the badge-access system or physical log storage meets the applicable source requirement (1-5 years depending on facility classification level).
+4. Spot-check that visitor records from the earliest required retention year are still retrievable and have not been destroyed prematurely.
+5. Identify any visitor records that have exceeded the required retention period and route them for authorized destruction per records-management policy.
+6. Document the visitor access records retention check, obtain FSO sign-off, and file it in the physical security records repository with the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
@@ -4722,11 +4722,12 @@
       <c r="F109" s="3" t="inlineStr"/>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>Pattern G — Retention / Disposal
-1. Identify all records that have passed their retention window per the applicable schedule (NARA, organizational records schedule, or the specific window cited in this task's Control ID(s)).
-2. Verify no candidate record is under legal hold, active investigation, or open POA&amp;M/incident reference.
-3. Execute disposal (secure deletion or destruction per the record's classification/handling requirement) for all cleared candidates.
-4. Log the disposal action (what, when, method, authorizer) in the repository location specified in the Task Index.</t>
+          <t>1. Pull the current data inventory/system of records listing all PII holdings and their assigned retention periods from the Data Owner's records schedule.
+2. Cross-check the PII data sets against the organization's NARA-approved or agency-specific records disposition schedule to confirm correct retention periods are applied.
+3. Query the storage location (file share, database, or records repository) for PII records that have reached or exceeded their scheduled retention period.
+4. Execute or witness the disposal action (secure deletion, degauss, shred, or sanitization per NIST SP 800-88) for records past their retention period and capture a certificate of destruction or deletion log.
+5. Confirm no PII record subject to a litigation hold or active investigation was included in the disposal action.
+6. Document the retention/disposal actions taken, obtain Information Owner/Steward sign-off, and file the disposal log and certificate in the data governance records repository with the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
@@ -4759,13 +4760,12 @@
       <c r="F110" s="3" t="inlineStr"/>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>Pattern B — Manual Review of a List or Log
-1. Pull the current list/log/record set for the review period.
-2. Pull the baseline or policy the list is being reviewed against (e.g., prior-cycle approved list, personnel roster, access policy).
-3. Compare the current list against the baseline line by line; flag every addition, removal, and unexplained entry.
-4. For each discrepancy, determine whether it is expected (documented change) or unexplained (potential finding).
-5. Update the baseline to reflect the newly reviewed-and-approved state.
-6. Log cycle completion in the repository location specified in the Task Index.</t>
+          <t>1. Pull the personnel security tracking system's reinvestigation due-date report listing all cleared personnel and their last investigation completion date.
+2. Calculate each individual's reinvestigation due date against the applicable periodic reinvestigation cycle (e.g., 5-year Tier 3/Secret, continuous evaluation enrollment) and identify anyone approaching or past due.
+3. Verify enrollment status in the Continuous Evaluation (CE) program via DISS/JPAS for personnel eligible for CE in lieu of a scheduled periodic reinvestigation.
+4. For personnel due, initiate the reinvestigation request in DISS (submit the e-QIP package) and record the submission date in the tracking system.
+5. Flag any overdue reinvestigation with no CE enrollment to the Personnel Security Officer for immediate action, including possible access suspension.
+6. Update the reinvestigation tracking log with submission/due dates, obtain PSO sign-off, and file it in the personnel security records repository with the reviewer's name and date.</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
@@ -4798,13 +4798,12 @@
       <c r="F111" s="3" t="inlineStr"/>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>Pattern A — Automated Monitoring / Scan Confirmation
-1. Confirm the automated tool/sensor executed on its scheduled cadence (per this task's Frequency in the Task Index).
-2. Review the tool's output/alert queue for the current cycle.
-3. Triage each new alert/finding: confirm true positive vs. false positive using the finding's supporting log/scan data.
-4. For each true-positive finding, determine CAT (I/II/III) per the finding's own severity source (STIG CAT rating, CVSS-derived CAT per `execution-plan/templates/VARIANCE-RISK-ACCEPTANCE-TEMPLATE.md`, or organizational policy for non-STIG/CVE findings).
-5. File or update the corresponding POA&amp;M/tracking entry for any open finding.
-6. Log cycle completion (date, reviewer, finding count, tracking IDs) in the repository location specified in the Task Index.</t>
+          <t>1. Coordinate with the certified TSCM team to schedule a physical and electronic Technical Surveillance Countermeasures Survey of the SCIF/sensitive space per the facility's TSCM policy interval.
+2. Conduct the physical inspection of the space (walls, ceiling, furniture, fixtures) for unauthorized devices, wiring anomalies, or tampering evidence.
+3. Perform RF spectrum analysis and telephone/data line sweeps using TSCM-certified equipment to detect unauthorized transmitters or eavesdropping devices.
+4. Cross-reference any Nessus scan results for unauthorized wireless access points or rogue devices detected on the facility's network segment during the same survey window.
+5. Document all findings, including any detected anomalies, in the TSCM survey report and immediately report confirmed technical penetrations to the ISSM/counterintelligence per incident procedures.
+6. Route the completed TSCM survey report through the PSO for review and retain it as a classified record, filing it in the facility security records repository with the surveyor's name and date.</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr">
